--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -76,7 +76,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -91,11 +91,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -136,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -144,9 +139,6 @@
       <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
@@ -156,7 +148,7 @@
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -167,21 +159,18 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -442,7 +431,7 @@
       <c r="K1" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="2">
         <v>45962.0</v>
       </c>
       <c r="M1" s="2">
@@ -484,306 +473,310 @@
       <c r="Y1" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>33624.74</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>49353.38</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>150019.57</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>35596.98</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <v>121861.65</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>217702.66</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>80860.65</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <v>56753.76</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>97057.61</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <v>117013.22</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>39130.08</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
         <v>24475.43</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="4">
         <v>50427.08</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="4">
         <v>215081.52</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="4">
         <v>378650.28</v>
       </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="Z2" s="6">
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="Z2" s="5">
         <f t="shared" ref="Z2:Z3" si="1">sum(N2:Y2)</f>
         <v>644158.88</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>2.0</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>2.0</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>5.0</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>2.0</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>9.0</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>12.0</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>5.0</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>4.0</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>5.0</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="6">
         <v>7.0</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="6">
         <v>7.0</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>3.0</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="6">
         <v>7.0</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="6">
         <v>13.0</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R3" s="6">
         <v>24.0</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="Z3" s="4">
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="Z3" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>16812.37</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>24676.69</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>30003.91</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>17798.49</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>13540.18</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>18141.89</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>16172.13</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>14188.44</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>19411.52</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>16716.17</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>5590.01</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
         <v>8158.48</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="4">
         <v>7203.87</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="4">
         <v>16544.73</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="4">
         <v>15777.09</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="5">
         <f t="shared" ref="Z4:Z6" si="2">average(N4:Y4)</f>
         <v>13175.23</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>0.3333</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.3571</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>0.3333</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>0.375</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>0.52</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>0.3333</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>0.1111</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>0.28</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>0.2353</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="8">
         <v>0.24</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <v>0.3333</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="9">
+      <c r="M5" s="9"/>
+      <c r="N5" s="8">
         <v>0.1818</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="8">
         <v>0.2308</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="8">
         <v>0.3529</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="8">
         <v>0.4167</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="8">
         <v>0.1923</v>
       </c>
-      <c r="S5" s="9"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="9">
+      <c r="S5" s="10">
+        <v>0.3333</v>
+      </c>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.2749</v>
+        <v>0.2846333333</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>0.5714</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>0.4167</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="11">
         <v>0.3182</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="11">
         <v>0.3333</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="11">
         <v>0.3429</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="11">
         <v>0.4348</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="11">
         <v>0.4468</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="11">
         <v>0.3462</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="11">
         <v>0.2456</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="11">
         <v>0.2203</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="11">
         <v>0.2537</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="11">
         <v>0.2593</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="11">
         <v>0.2368</v>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="11">
         <v>0.2308</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="11">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="11">
         <v>0.3393</v>
       </c>
-      <c r="R6" s="13">
+      <c r="R6" s="11">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14">
+      <c r="S6" s="12">
+        <v>0.2673</v>
+      </c>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2699</v>
+        <v>0.2694666667</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -822,7 +815,7 @@
       <c r="K9" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>45962.0</v>
       </c>
       <c r="M9" s="2">
@@ -864,330 +857,334 @@
       <c r="Y9" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z9" s="4" t="s">
+      <c r="Z9" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>26439.71</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>51542.87</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>75885.54</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>103291.98</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>153828.56</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>142652.92</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>63419.5</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>131500.17</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="4">
         <v>131200.28</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="4">
         <v>28825.49</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="4">
         <v>10448.87</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="4">
         <v>90672.39</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="4">
         <v>34294.16</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10" s="4">
         <v>65730.26</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q10" s="4">
         <v>349069.93</v>
       </c>
-      <c r="R10" s="5">
+      <c r="R10" s="4">
         <v>118400.53</v>
       </c>
-      <c r="S10" s="5"/>
-      <c r="W10" s="15"/>
-      <c r="Z10" s="6">
+      <c r="S10" s="4"/>
+      <c r="W10" s="13"/>
+      <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>2.0</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>5.0</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>10.0</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>11.0</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>20.0</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>8.0</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <v>8.0</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <v>8.0</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="6">
         <v>15.0</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="6">
         <v>9.0</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="6">
         <v>3.0</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="6">
         <v>6.0</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="6">
         <v>11.0</v>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="6">
         <v>10.0</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="6">
         <v>30.0</v>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="6">
         <v>9.0</v>
       </c>
-      <c r="S11" s="7"/>
-      <c r="W11" s="15"/>
-      <c r="Z11" s="4">
+      <c r="S11" s="6"/>
+      <c r="W11" s="13"/>
+      <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>13219.86</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>10308.57</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>7588.55</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>9390.18</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>7691.43</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>17831.62</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <v>7927.44</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>16437.52</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="4">
         <v>8746.69</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="4">
         <v>3202.83</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="4">
         <v>3482.96</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="4">
         <v>15112.07</v>
       </c>
-      <c r="O12" s="5">
+      <c r="O12" s="4">
         <v>3117.65</v>
       </c>
-      <c r="P12" s="5">
+      <c r="P12" s="4">
         <v>6573.03</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="Q12" s="4">
         <v>11635.66</v>
       </c>
-      <c r="R12" s="5">
+      <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="15"/>
-      <c r="Z12" s="6">
+      <c r="W12" s="13"/>
+      <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>0.5</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>0.2381</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>0.375</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <v>0.4231</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>0.4333</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>0.4231</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>0.25</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <v>0.2632</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>0.4211</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="8">
         <v>0.2973</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="8">
         <v>0.2727</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="8">
         <v>0.6429</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="8">
         <v>0.5385</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="8">
         <v>0.2759</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="8">
         <v>0.3429</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="8">
         <v>0.3333</v>
       </c>
-      <c r="R13" s="11">
+      <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="13"/>
-      <c r="T13" s="16"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
+      <c r="S13" s="12">
+        <v>0.0526</v>
+      </c>
+      <c r="T13" s="14"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11">
         <v>0.5161</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="11">
         <v>0.3333</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="11">
         <v>0.34</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="11">
         <v>0.3521</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="11">
         <v>0.4125</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="11">
         <v>0.4321</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="11">
         <v>0.369</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="11">
         <v>0.3194</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="11">
         <v>0.2969</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="11">
         <v>0.32</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="11">
         <v>0.3205</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="11">
         <v>0.3571</v>
       </c>
-      <c r="O14" s="13">
+      <c r="O14" s="11">
         <v>0.449</v>
       </c>
-      <c r="P14" s="13">
+      <c r="P14" s="11">
         <v>0.4182</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="Q14" s="11">
         <v>0.3269</v>
       </c>
-      <c r="R14" s="13">
+      <c r="R14" s="11">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="13"/>
-      <c r="T14" s="16"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14">
+      <c r="S14" s="12">
+        <v>0.2044</v>
+      </c>
+      <c r="T14" s="14"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2711</v>
+        <v>0.23775</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="S15" s="14"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
@@ -1223,7 +1220,7 @@
       <c r="K17" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="2">
         <v>45962.0</v>
       </c>
       <c r="M17" s="2">
@@ -1265,281 +1262,283 @@
       <c r="Y17" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z17" s="4" t="s">
+      <c r="Z17" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>31222.74</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>1972.5</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>165667.1</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>200911.27</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="4">
         <v>46590.51</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="4">
         <v>13253.11</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="4">
         <v>182255.48</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="4">
         <v>128036.34</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="4">
         <v>64847.69</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N18" s="4">
         <v>65950.63</v>
       </c>
-      <c r="O18" s="5">
+      <c r="O18" s="4">
         <v>14994.71</v>
       </c>
-      <c r="P18" s="5">
+      <c r="P18" s="4">
         <v>76787.72</v>
       </c>
-      <c r="Q18" s="5">
+      <c r="Q18" s="4">
         <v>262251.4</v>
       </c>
-      <c r="R18" s="5">
+      <c r="R18" s="4">
         <v>147003.47</v>
       </c>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="Z18" s="6">
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="Z18" s="5">
         <f t="shared" ref="Z18:Z19" si="4">sum(N18:Y18)</f>
         <v>566987.93</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <v>1.0</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>1.0</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="6">
         <v>7.0</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>5.0</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="6">
         <v>8.0</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="6">
         <v>6.0</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="6">
         <v>16.0</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="6">
         <v>8.0</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="6">
         <v>4.0</v>
       </c>
-      <c r="N19" s="7">
+      <c r="N19" s="6">
         <v>4.0</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O19" s="6">
         <v>1.0</v>
       </c>
-      <c r="P19" s="7">
+      <c r="P19" s="6">
         <v>7.0</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="Q19" s="6">
         <v>22.0</v>
       </c>
-      <c r="R19" s="7">
+      <c r="R19" s="6">
         <v>7.0</v>
       </c>
-      <c r="S19" s="7"/>
-      <c r="Z19" s="4">
+      <c r="S19" s="6"/>
+      <c r="Z19" s="3">
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>31222.74</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>1972.5</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>23666.73</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>40182.25</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="4">
         <v>5823.81</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="4">
         <v>2208.85</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="4">
         <v>11390.97</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="4">
         <v>16004.54</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="4">
         <v>16211.92</v>
       </c>
-      <c r="N20" s="5">
+      <c r="N20" s="4">
         <v>16487.66</v>
       </c>
-      <c r="O20" s="5">
+      <c r="O20" s="4">
         <v>14994.71</v>
       </c>
-      <c r="P20" s="5">
+      <c r="P20" s="4">
         <v>10969.67</v>
       </c>
-      <c r="Q20" s="5">
+      <c r="Q20" s="4">
         <v>11920.52</v>
       </c>
-      <c r="R20" s="5">
+      <c r="R20" s="4">
         <v>21000.5</v>
       </c>
-      <c r="Z20" s="6">
+      <c r="Z20" s="5">
         <f>average(N20:Y20)</f>
         <v>15074.612</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="9">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="8">
         <v>0.6667</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="8">
         <v>0.4286</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>0.4286</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>0.5</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="8">
         <v>0.5333</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="8">
         <v>0.381</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="8">
         <v>0.2963</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="8">
         <v>0.3571</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="8">
         <v>0.33</v>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="8">
         <v>0.2308</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="8">
         <v>0.1613</v>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="8">
         <v>0.3673</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="Q21" s="8">
         <v>0.22</v>
       </c>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="4"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="13">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11">
         <v>0.5</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="11">
         <v>0.5625</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="11">
         <v>0.5714</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="11">
         <v>0.4815</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="11">
         <v>0.4634</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="11">
         <v>0.4898</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="11">
         <v>0.463</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="11">
         <v>0.377</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="11">
         <v>0.3387</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="11">
         <v>0.3265</v>
       </c>
-      <c r="O22" s="13">
+      <c r="O22" s="11">
         <v>0.3056</v>
       </c>
-      <c r="P22" s="13">
+      <c r="P22" s="11">
         <v>0.2075</v>
       </c>
-      <c r="Q22" s="13">
+      <c r="Q22" s="11">
         <v>0.2615</v>
       </c>
-      <c r="R22" s="13">
+      <c r="R22" s="11">
         <v>0.232</v>
       </c>
-      <c r="S22" s="13"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14">
+      <c r="S22" s="12">
+        <v>0.181</v>
+      </c>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.232</v>
+        <v>0.2065</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1578,7 +1577,7 @@
       <c r="K25" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="2">
         <v>45962.0</v>
       </c>
       <c r="M25" s="2">
@@ -1620,310 +1619,314 @@
       <c r="Y25" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z25" s="4" t="s">
+      <c r="Z25" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>18650.58</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>30930.58</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>10220.61</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <v>40940.34</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>31725.85</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>59653.44</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="4">
         <v>52341.19</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="4">
         <v>43968.35</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="4">
         <v>55035.51</v>
       </c>
-      <c r="L26" s="5">
+      <c r="L26" s="4">
         <v>30872.18</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26" s="4">
         <v>5421.62</v>
       </c>
-      <c r="N26" s="5">
+      <c r="N26" s="4">
         <v>9080.08</v>
       </c>
-      <c r="O26" s="5">
+      <c r="O26" s="4">
         <v>5713.65</v>
       </c>
-      <c r="P26" s="5">
+      <c r="P26" s="4">
         <v>55012.85</v>
       </c>
-      <c r="Q26" s="5">
+      <c r="Q26" s="4">
         <v>13845.3</v>
       </c>
-      <c r="R26" s="5">
+      <c r="R26" s="4">
         <v>88880.21</v>
       </c>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="Z26" s="6">
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="Z26" s="5">
         <f t="shared" ref="Z26:Z27" si="5">sum(N26:Y26)</f>
         <v>172532.09</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <v>1.0</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>5.0</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="6">
         <v>2.0</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>3.0</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="6">
         <v>13.0</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>13.0</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="6">
         <v>10.0</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="6">
         <v>13.0</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="6">
         <v>16.0</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="6">
         <v>6.0</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="6">
         <v>2.0</v>
       </c>
-      <c r="N27" s="7">
+      <c r="N27" s="6">
         <v>7.0</v>
       </c>
-      <c r="O27" s="7">
+      <c r="O27" s="6">
         <v>2.0</v>
       </c>
-      <c r="P27" s="7">
+      <c r="P27" s="6">
         <v>14.0</v>
       </c>
-      <c r="Q27" s="7">
+      <c r="Q27" s="6">
         <v>12.0</v>
       </c>
-      <c r="R27" s="7">
+      <c r="R27" s="6">
         <v>10.0</v>
       </c>
-      <c r="S27" s="7"/>
-      <c r="W27" s="15"/>
-      <c r="Z27" s="4">
+      <c r="S27" s="6"/>
+      <c r="W27" s="13"/>
+      <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>18650.58</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>6186.12</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>5110.3</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>13646.78</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>2440.45</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>4588.73</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="4">
         <v>5234.12</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="4">
         <v>3382.18</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="4">
         <v>3439.72</v>
       </c>
-      <c r="L28" s="5">
+      <c r="L28" s="4">
         <v>5145.36</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28" s="4">
         <v>2710.81</v>
       </c>
-      <c r="N28" s="5">
+      <c r="N28" s="4">
         <v>1297.15</v>
       </c>
-      <c r="O28" s="5">
+      <c r="O28" s="4">
         <v>2856.82</v>
       </c>
-      <c r="P28" s="5">
+      <c r="P28" s="4">
         <v>3929.49</v>
       </c>
-      <c r="Q28" s="5">
+      <c r="Q28" s="4">
         <v>1153.77</v>
       </c>
-      <c r="R28" s="5">
+      <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="16"/>
-      <c r="W28" s="15"/>
-      <c r="Z28" s="6">
+      <c r="T28" s="14"/>
+      <c r="W28" s="13"/>
+      <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="9">
+      <c r="B29" s="9"/>
+      <c r="C29" s="8">
         <v>0.2143</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>0.5556</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <v>0.25</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="8">
         <v>0.2632</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="8">
         <v>0.3714</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="8">
         <v>0.6667</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="8">
         <v>0.2222</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="8">
         <v>0.4</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="8">
         <v>0.3636</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="8">
         <v>0.1852</v>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="8">
         <v>0.1333</v>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="8">
         <v>0.2381</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="8">
         <v>0.2308</v>
       </c>
-      <c r="P29" s="11">
+      <c r="P29" s="8">
         <v>0.4</v>
       </c>
-      <c r="Q29" s="11">
+      <c r="Q29" s="8">
         <v>0.2759</v>
       </c>
-      <c r="R29" s="13"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="4"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="12">
+        <v>0.0769</v>
+      </c>
+      <c r="T29" s="16"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="13">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11">
         <v>0.1333</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="11">
         <v>0.1667</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0.3514</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="11">
         <v>0.375</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="11">
         <v>0.3778</v>
       </c>
-      <c r="H30" s="13">
+      <c r="H30" s="11">
         <v>0.3226</v>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="11">
         <v>0.4359</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="11">
         <v>0.4286</v>
       </c>
-      <c r="K30" s="13">
+      <c r="K30" s="11">
         <v>0.4366</v>
       </c>
-      <c r="L30" s="13">
+      <c r="L30" s="11">
         <v>0.3457</v>
       </c>
-      <c r="M30" s="13">
+      <c r="M30" s="11">
         <v>0.3222</v>
       </c>
-      <c r="N30" s="13">
+      <c r="N30" s="11">
         <v>0.2568</v>
       </c>
-      <c r="O30" s="13">
+      <c r="O30" s="11">
         <v>0.1905</v>
       </c>
-      <c r="P30" s="13">
+      <c r="P30" s="11">
         <v>0.2281</v>
       </c>
-      <c r="Q30" s="13">
+      <c r="Q30" s="11">
         <v>0.3243</v>
       </c>
-      <c r="R30" s="13">
+      <c r="R30" s="11">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="13"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="14">
+      <c r="S30" s="12">
+        <v>0.2759</v>
+      </c>
+      <c r="T30" s="16"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="11"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+      <c r="Y30" s="11"/>
+      <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.3297</v>
+        <v>0.3028</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -1962,7 +1965,7 @@
       <c r="K33" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="2">
         <v>45962.0</v>
       </c>
       <c r="M33" s="2">
@@ -2004,313 +2007,317 @@
       <c r="Y33" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z33" s="4" t="s">
+      <c r="Z33" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>55872.76</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="4">
         <v>2336.73</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="4">
         <v>33592.39</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="4">
         <v>21413.67</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="4">
         <v>186331.34</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="4">
         <v>163356.3</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="4">
         <v>93899.31</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="4">
         <v>95663.96</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J34" s="4">
         <v>52111.35</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K34" s="4">
         <v>205694.01</v>
       </c>
-      <c r="L34" s="5">
+      <c r="L34" s="4">
         <v>38500.4</v>
       </c>
-      <c r="M34" s="5">
+      <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="15"/>
-      <c r="O34" s="5">
+      <c r="N34" s="13"/>
+      <c r="O34" s="4">
         <v>8067.86</v>
       </c>
-      <c r="P34" s="5">
+      <c r="P34" s="4">
         <v>108802.59</v>
       </c>
-      <c r="Q34" s="5">
+      <c r="Q34" s="4">
         <v>149911.53</v>
       </c>
-      <c r="R34" s="5">
+      <c r="R34" s="4">
         <v>158044.97</v>
       </c>
-      <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
-      <c r="Z34" s="6">
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+      <c r="Z34" s="5">
         <f t="shared" ref="Z34:Z35" si="6">sum(N34:Y34)</f>
         <v>424826.95</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="6">
         <v>2.0</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>2.0</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="6">
         <v>1.0</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="6">
         <v>8.0</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="6">
         <v>13.0</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="6">
         <v>8.0</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="6">
         <v>10.0</v>
       </c>
-      <c r="I35" s="7">
+      <c r="I35" s="6">
         <v>2.0</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="6">
         <v>4.0</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="6">
         <v>17.0</v>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="6">
         <v>5.0</v>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="6">
         <v>8.0</v>
       </c>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <v>1.0</v>
       </c>
-      <c r="P35" s="7">
+      <c r="P35" s="6">
         <v>9.0</v>
       </c>
-      <c r="Q35" s="7">
+      <c r="Q35" s="6">
         <v>16.0</v>
       </c>
-      <c r="R35" s="7">
+      <c r="R35" s="6">
         <v>9.0</v>
       </c>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="Z35" s="4">
+      <c r="S35" s="6"/>
+      <c r="T35" s="6"/>
+      <c r="Z35" s="3">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>27936.38</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="4">
         <v>1168.36</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="4">
         <v>33592.39</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="4">
         <v>2676.71</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="4">
         <v>14333.18</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="4">
         <v>20419.54</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36" s="4">
         <v>9389.93</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="4">
         <v>47831.98</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36" s="4">
         <v>13027.84</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K36" s="4">
         <v>12099.65</v>
       </c>
-      <c r="L36" s="5">
+      <c r="L36" s="4">
         <v>7700.08</v>
       </c>
-      <c r="M36" s="5">
+      <c r="M36" s="4">
         <v>1857.67</v>
       </c>
-      <c r="O36" s="5">
+      <c r="O36" s="4">
         <v>8067.86</v>
       </c>
-      <c r="P36" s="5">
+      <c r="P36" s="4">
         <v>12089.18</v>
       </c>
-      <c r="Q36" s="5">
+      <c r="Q36" s="4">
         <v>9369.47</v>
       </c>
-      <c r="R36" s="5">
+      <c r="R36" s="4">
         <v>17560.55</v>
       </c>
-      <c r="Z36" s="6">
+      <c r="Z36" s="5">
         <f>average(N36:Y36)</f>
         <v>11771.765</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="8">
         <v>0.2</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="8">
         <v>0.4286</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>0.4211</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="8">
         <v>0.4091</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="8">
         <v>0.3793</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="8">
         <v>0.7143</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="8">
         <v>0.5</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="8">
         <v>0.2857</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="8">
         <v>0.625</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="8">
         <v>0.2609</v>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="8">
         <v>0.6364</v>
       </c>
-      <c r="M37" s="10"/>
-      <c r="N37" s="9">
+      <c r="M37" s="9"/>
+      <c r="N37" s="8">
         <v>0.1429</v>
       </c>
-      <c r="O37" s="11">
+      <c r="O37" s="8">
         <v>0.3333</v>
       </c>
-      <c r="P37" s="11">
+      <c r="P37" s="8">
         <v>0.3333</v>
       </c>
-      <c r="Q37" s="9">
+      <c r="Q37" s="8">
         <v>0.303</v>
       </c>
-      <c r="R37" s="13">
+      <c r="R37" s="11">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="13"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="4"/>
+      <c r="S37" s="12">
+        <v>0.3333</v>
+      </c>
+      <c r="T37" s="11"/>
+      <c r="U37" s="11"/>
+      <c r="V37" s="11"/>
+      <c r="W37" s="11"/>
+      <c r="X37" s="11"/>
+      <c r="Y37" s="11"/>
+      <c r="Z37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="11">
         <v>0.4375</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="11">
         <v>0.4</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="11">
         <v>0.4</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <v>0.4</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="11">
         <v>0.4167</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="11">
         <v>0.4</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="11">
         <v>0.4211</v>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="11">
         <v>0.451</v>
       </c>
-      <c r="J38" s="13">
+      <c r="J38" s="11">
         <v>0.5161</v>
       </c>
-      <c r="K38" s="13">
+      <c r="K38" s="11">
         <v>0.5128</v>
       </c>
-      <c r="L38" s="13">
+      <c r="L38" s="11">
         <v>0.3913</v>
       </c>
-      <c r="M38" s="13">
+      <c r="M38" s="11">
         <v>0.46</v>
       </c>
-      <c r="N38" s="13">
+      <c r="N38" s="11">
         <v>0.325</v>
       </c>
-      <c r="O38" s="13">
+      <c r="O38" s="11">
         <v>0.3333</v>
       </c>
-      <c r="P38" s="13">
+      <c r="P38" s="11">
         <v>0.2564</v>
       </c>
-      <c r="Q38" s="13">
+      <c r="Q38" s="11">
         <v>0.3238</v>
       </c>
-      <c r="R38" s="13">
+      <c r="R38" s="11">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="13"/>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
-      <c r="X38" s="14"/>
-      <c r="Y38" s="14"/>
-      <c r="Z38" s="14">
+      <c r="S38" s="12">
+        <v>0.2024</v>
+      </c>
+      <c r="T38" s="11"/>
+      <c r="U38" s="11"/>
+      <c r="V38" s="11"/>
+      <c r="W38" s="11"/>
+      <c r="X38" s="11"/>
+      <c r="Y38" s="11"/>
+      <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2432</v>
+        <v>0.2228</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2349,7 +2356,7 @@
       <c r="K41" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L41" s="4" t="s">
+      <c r="L41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="M41" s="2">
@@ -2391,149 +2398,153 @@
       <c r="Y41" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z41" s="4" t="s">
+      <c r="Z41" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P42" s="5">
+      <c r="P42" s="4">
         <v>9374.61</v>
       </c>
-      <c r="Q42" s="5">
+      <c r="Q42" s="4">
         <v>123258.92</v>
       </c>
-      <c r="R42" s="5">
+      <c r="R42" s="4">
         <v>152476.32</v>
       </c>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-      <c r="Z42" s="6">
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="Z42" s="5">
         <f t="shared" ref="Z42:Z43" si="7">sum(N42:Y42)</f>
         <v>285109.85</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="7">
+      <c r="P43" s="6">
         <v>5.0</v>
       </c>
-      <c r="Q43" s="7">
+      <c r="Q43" s="6">
         <v>12.0</v>
       </c>
-      <c r="R43" s="7">
+      <c r="R43" s="6">
         <v>12.0</v>
       </c>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="Z43" s="4">
+      <c r="S43" s="6"/>
+      <c r="T43" s="6"/>
+      <c r="Z43" s="3">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="15"/>
-      <c r="P44" s="5">
+      <c r="L44" s="13"/>
+      <c r="P44" s="4">
         <v>1874.92</v>
       </c>
-      <c r="Q44" s="5">
+      <c r="Q44" s="4">
         <v>10271.58</v>
       </c>
-      <c r="R44" s="5">
+      <c r="R44" s="4">
         <v>12706.36</v>
       </c>
-      <c r="Z44" s="6">
+      <c r="Z44" s="5">
         <f>average(N44:Y44)</f>
         <v>8284.286667</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="9">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="8">
         <v>0.1429</v>
       </c>
-      <c r="P45" s="11">
+      <c r="P45" s="8">
         <v>0.3696</v>
       </c>
-      <c r="Q45" s="11">
+      <c r="Q45" s="8">
         <v>0.2222</v>
       </c>
-      <c r="R45" s="11">
+      <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="13"/>
-      <c r="T45" s="14"/>
-      <c r="U45" s="14"/>
-      <c r="V45" s="14"/>
-      <c r="W45" s="14"/>
-      <c r="X45" s="14"/>
-      <c r="Y45" s="14"/>
-      <c r="Z45" s="14"/>
+      <c r="S45" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="T45" s="11"/>
+      <c r="U45" s="11"/>
+      <c r="V45" s="11"/>
+      <c r="W45" s="11"/>
+      <c r="X45" s="11"/>
+      <c r="Y45" s="11"/>
+      <c r="Z45" s="11"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
-      <c r="L46" s="13"/>
-      <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="13">
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11">
         <v>0.1111</v>
       </c>
-      <c r="Q46" s="13">
+      <c r="Q46" s="11">
         <v>0.2828</v>
       </c>
-      <c r="R46" s="13">
+      <c r="R46" s="11">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="13"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="14"/>
-      <c r="W46" s="14"/>
-      <c r="X46" s="14"/>
-      <c r="Y46" s="14"/>
-      <c r="Z46" s="14">
+      <c r="S46" s="12">
+        <v>0.2157</v>
+      </c>
+      <c r="T46" s="11"/>
+      <c r="U46" s="11"/>
+      <c r="V46" s="11"/>
+      <c r="W46" s="11"/>
+      <c r="X46" s="11"/>
+      <c r="Y46" s="11"/>
+      <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2667</v>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
@@ -2570,7 +2581,7 @@
       <c r="K49" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L49" s="4" t="s">
+      <c r="L49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="M49" s="2">
@@ -2612,139 +2623,143 @@
       <c r="Y49" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z49" s="4" t="s">
+      <c r="Z49" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P50" s="5">
+      <c r="P50" s="4">
         <v>816.62</v>
       </c>
-      <c r="Q50" s="5">
+      <c r="Q50" s="4">
         <v>124770.34</v>
       </c>
-      <c r="R50" s="5">
+      <c r="R50" s="4">
         <v>78978.19</v>
       </c>
-      <c r="S50" s="5"/>
-      <c r="T50" s="5"/>
-      <c r="Z50" s="6">
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="Z50" s="5">
         <f t="shared" ref="Z50:Z51" si="8">sum(N50:Y50)</f>
         <v>204565.15</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P51" s="7">
+      <c r="P51" s="6">
         <v>2.0</v>
       </c>
-      <c r="Q51" s="7">
+      <c r="Q51" s="6">
         <v>13.0</v>
       </c>
-      <c r="R51" s="7">
+      <c r="R51" s="6">
         <v>15.0</v>
       </c>
-      <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
-      <c r="Z51" s="4">
+      <c r="S51" s="6"/>
+      <c r="T51" s="6"/>
+      <c r="Z51" s="3">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="5">
+      <c r="P52" s="4">
         <v>408.31</v>
       </c>
-      <c r="Q52" s="5">
+      <c r="Q52" s="4">
         <v>9597.72</v>
       </c>
-      <c r="R52" s="5">
+      <c r="R52" s="4">
         <v>5265.21</v>
       </c>
-      <c r="Z52" s="6">
+      <c r="Z52" s="5">
         <f>average(N52:Y52)</f>
         <v>5090.413333</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="11">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="8">
         <v>0.3778</v>
       </c>
-      <c r="Q53" s="11">
+      <c r="Q53" s="8">
         <v>0.2222</v>
       </c>
-      <c r="R53" s="11">
+      <c r="R53" s="8">
         <v>0.2857</v>
       </c>
-      <c r="S53" s="13"/>
-      <c r="T53" s="14"/>
-      <c r="U53" s="14"/>
-      <c r="V53" s="14"/>
-      <c r="W53" s="14"/>
-      <c r="X53" s="14"/>
-      <c r="Y53" s="14"/>
-      <c r="Z53" s="14"/>
+      <c r="S53" s="12">
+        <v>0.0333</v>
+      </c>
+      <c r="T53" s="11"/>
+      <c r="U53" s="11"/>
+      <c r="V53" s="11"/>
+      <c r="W53" s="11"/>
+      <c r="X53" s="11"/>
+      <c r="Y53" s="11"/>
+      <c r="Z53" s="11"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="13"/>
-      <c r="Q54" s="13">
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11">
         <v>0.2727</v>
       </c>
-      <c r="R54" s="13">
+      <c r="R54" s="11">
         <v>0.296</v>
       </c>
-      <c r="S54" s="13"/>
-      <c r="T54" s="14"/>
-      <c r="U54" s="14"/>
-      <c r="V54" s="14"/>
-      <c r="W54" s="14"/>
-      <c r="X54" s="14"/>
-      <c r="Y54" s="14"/>
-      <c r="Z54" s="14">
+      <c r="S54" s="12">
+        <v>0.2222</v>
+      </c>
+      <c r="T54" s="11"/>
+      <c r="U54" s="11"/>
+      <c r="V54" s="11"/>
+      <c r="W54" s="11"/>
+      <c r="X54" s="11"/>
+      <c r="Y54" s="11"/>
+      <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.296</v>
+        <v>0.2591</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -2761,7 +2776,7 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
-      <c r="L57" s="4"/>
+      <c r="L57" s="3"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -2775,109 +2790,109 @@
       <c r="W57" s="2"/>
       <c r="X57" s="2"/>
       <c r="Y57" s="2"/>
-      <c r="Z57" s="4"/>
+      <c r="Z57" s="3"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="4"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
-      <c r="L58" s="15"/>
-      <c r="M58" s="5"/>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="5"/>
-      <c r="R58" s="5"/>
-      <c r="S58" s="5"/>
-      <c r="T58" s="5"/>
-      <c r="Z58" s="6"/>
+      <c r="A58" s="3"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="Z58" s="5"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="4"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="M59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="7"/>
-      <c r="Q59" s="7"/>
-      <c r="R59" s="7"/>
-      <c r="S59" s="7"/>
-      <c r="T59" s="7"/>
-      <c r="Z59" s="4"/>
+      <c r="A59" s="3"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="6"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="6"/>
+      <c r="T59" s="6"/>
+      <c r="Z59" s="3"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="4"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="M60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
-      <c r="R60" s="5"/>
-      <c r="Z60" s="6"/>
+      <c r="A60" s="3"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="Z60" s="5"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="8"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="13"/>
-      <c r="N61" s="13"/>
-      <c r="O61" s="13"/>
-      <c r="P61" s="13"/>
-      <c r="Q61" s="13"/>
-      <c r="R61" s="13"/>
-      <c r="S61" s="14"/>
-      <c r="T61" s="14"/>
-      <c r="U61" s="14"/>
-      <c r="V61" s="14"/>
-      <c r="W61" s="14"/>
-      <c r="X61" s="14"/>
-      <c r="Y61" s="14"/>
-      <c r="Z61" s="4"/>
+      <c r="A61" s="7"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="11"/>
+      <c r="O61" s="11"/>
+      <c r="P61" s="11"/>
+      <c r="Q61" s="11"/>
+      <c r="R61" s="11"/>
+      <c r="S61" s="11"/>
+      <c r="T61" s="11"/>
+      <c r="U61" s="11"/>
+      <c r="V61" s="11"/>
+      <c r="W61" s="11"/>
+      <c r="X61" s="11"/>
+      <c r="Y61" s="11"/>
+      <c r="Z61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="13"/>
-      <c r="Q62" s="13"/>
-      <c r="R62" s="13"/>
-      <c r="S62" s="14"/>
-      <c r="T62" s="14"/>
-      <c r="U62" s="14"/>
-      <c r="V62" s="14"/>
-      <c r="W62" s="14"/>
-      <c r="X62" s="14"/>
-      <c r="Y62" s="14"/>
-      <c r="Z62" s="4"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="11"/>
+      <c r="O62" s="11"/>
+      <c r="P62" s="11"/>
+      <c r="Q62" s="11"/>
+      <c r="R62" s="11"/>
+      <c r="S62" s="11"/>
+      <c r="T62" s="11"/>
+      <c r="U62" s="11"/>
+      <c r="V62" s="11"/>
+      <c r="W62" s="11"/>
+      <c r="X62" s="11"/>
+      <c r="Y62" s="11"/>
+      <c r="Z62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="B63" s="2"/>
@@ -2890,7 +2905,7 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="4"/>
+      <c r="L63" s="3"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -2904,7 +2919,7 @@
       <c r="W63" s="2"/>
       <c r="X63" s="2"/>
       <c r="Y63" s="2"/>
-      <c r="Z63" s="4"/>
+      <c r="Z63" s="3"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="2">
@@ -2937,7 +2952,7 @@
       <c r="K64" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L64" s="4" t="s">
+      <c r="L64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="M64" s="2">
@@ -2979,603 +2994,508 @@
       <c r="Y64" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z64" s="4" t="s">
+      <c r="Z64" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B65" s="6">
-        <f t="shared" ref="B65:Y65" si="9">sum(B58,B50,B42,B34,B26,B18,B10,B2)</f>
+      <c r="B65" s="5">
+        <f t="shared" ref="B65:R65" si="9">sum(B58,B50,B42,B34,B26,B18,B10,B2)</f>
         <v>89497.5</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="5">
         <f t="shared" si="9"/>
         <v>96780.4</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="5">
         <f t="shared" si="9"/>
         <v>266085.41</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E65" s="5">
         <f t="shared" si="9"/>
         <v>174339.54</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="5">
         <f t="shared" si="9"/>
         <v>454397.81</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="5">
         <f t="shared" si="9"/>
         <v>732280.47</v>
       </c>
-      <c r="H65" s="6">
+      <c r="H65" s="5">
         <f t="shared" si="9"/>
         <v>577977.59</v>
       </c>
-      <c r="I65" s="6">
+      <c r="I65" s="5">
         <f t="shared" si="9"/>
         <v>314768.92</v>
       </c>
-      <c r="J65" s="6">
+      <c r="J65" s="5">
         <f t="shared" si="9"/>
         <v>337890.59</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="5">
         <f t="shared" si="9"/>
         <v>691198.5</v>
       </c>
-      <c r="L65" s="6">
+      <c r="L65" s="5">
         <f t="shared" si="9"/>
         <v>265364.49</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="5">
         <f t="shared" si="9"/>
         <v>120054.95</v>
       </c>
-      <c r="N65" s="6">
+      <c r="N65" s="5">
         <f t="shared" si="9"/>
         <v>165703.1</v>
       </c>
-      <c r="O65" s="6">
+      <c r="O65" s="5">
         <f t="shared" si="9"/>
         <v>63070.38</v>
       </c>
-      <c r="P65" s="6">
+      <c r="P65" s="5">
         <f t="shared" si="9"/>
         <v>366951.73</v>
       </c>
-      <c r="Q65" s="6">
+      <c r="Q65" s="5">
         <f t="shared" si="9"/>
         <v>1238188.94</v>
       </c>
-      <c r="R65" s="6">
+      <c r="R65" s="5">
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T65" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="U65" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="V65" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W65" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X65" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Y65" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Z65" s="6">
+      <c r="S65" s="18"/>
+      <c r="T65" s="18"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="5">
         <f>sum(N65:Y65)</f>
         <v>2956348.12</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B66" s="6">
-        <f t="shared" ref="B66:Z66" si="10">average(B58,B50,B42,B34,B26,B18,B10,B2)</f>
+      <c r="B66" s="5">
+        <f t="shared" ref="B66:R66" si="10">average(B58,B50,B42,B34,B26,B18,B10,B2)</f>
         <v>44748.75</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="5">
         <f t="shared" si="10"/>
         <v>24195.1</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="5">
         <f t="shared" si="10"/>
         <v>66521.3525</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="5">
         <f t="shared" si="10"/>
         <v>34867.908</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="5">
         <f t="shared" si="10"/>
         <v>90879.562</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="5">
         <f t="shared" si="10"/>
         <v>146456.094</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="5">
         <f t="shared" si="10"/>
         <v>115595.518</v>
       </c>
-      <c r="I66" s="6">
+      <c r="I66" s="5">
         <f t="shared" si="10"/>
         <v>62953.784</v>
       </c>
-      <c r="J66" s="6">
+      <c r="J66" s="5">
         <f t="shared" si="10"/>
         <v>67578.118</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="5">
         <f t="shared" si="10"/>
         <v>138239.7</v>
       </c>
-      <c r="L66" s="6">
+      <c r="L66" s="5">
         <f t="shared" si="10"/>
         <v>53072.898</v>
       </c>
-      <c r="M66" s="6">
+      <c r="M66" s="5">
         <f t="shared" si="10"/>
         <v>24010.99</v>
       </c>
-      <c r="N66" s="6">
+      <c r="N66" s="5">
         <f t="shared" si="10"/>
         <v>55234.36667</v>
       </c>
-      <c r="O66" s="6">
+      <c r="O66" s="5">
         <f t="shared" si="10"/>
         <v>15767.595</v>
       </c>
-      <c r="P66" s="6">
+      <c r="P66" s="5">
         <f t="shared" si="10"/>
         <v>52421.67571</v>
       </c>
-      <c r="Q66" s="6">
+      <c r="Q66" s="5">
         <f t="shared" si="10"/>
         <v>176884.1343</v>
       </c>
-      <c r="R66" s="6">
+      <c r="R66" s="5">
         <f t="shared" si="10"/>
         <v>160347.71</v>
       </c>
-      <c r="S66" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T66" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U66" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V66" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W66" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X66" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y66" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z66" s="6">
-        <f t="shared" si="10"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="5">
+        <f>average(Z58,Z50,Z42,Z34,Z26,Z18,Z10,Z2)</f>
         <v>422335.4457</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="21">
+      <c r="B67" s="19">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="21">
+      <c r="C67" s="19">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="21">
+      <c r="D67" s="19">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="21">
+      <c r="E67" s="19">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="21">
+      <c r="F67" s="19">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="21">
+      <c r="G67" s="19">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="21">
+      <c r="H67" s="19">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="21">
+      <c r="I67" s="19">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="21">
+      <c r="J67" s="19">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="21">
+      <c r="K67" s="19">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="21">
+      <c r="L67" s="19">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="21">
+      <c r="M67" s="19">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="21">
+      <c r="N67" s="19">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="21">
+      <c r="O67" s="19">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="21">
+      <c r="P67" s="19">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="21">
+      <c r="Q67" s="19">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="21">
+      <c r="R67" s="19">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
-      <c r="S67" s="4">
-        <f t="shared" ref="S67:Y67" si="12">sum(S59,S51,S43,S35,S27,S19,S11,S3)</f>
-        <v>0</v>
-      </c>
-      <c r="T67" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U67" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="V67" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="W67" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="X67" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Y67" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Z67" s="21">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="19">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B68" s="6">
-        <f t="shared" ref="B68:Y68" si="13">AVERAGE(B60,B52,B44,B36,B28,B20,B12,B4)</f>
+      <c r="B68" s="5">
+        <f t="shared" ref="B68:R68" si="12">AVERAGE(B60,B52,B44,B36,B28,B20,B12,B4)</f>
         <v>22374.375</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="5">
+        <f t="shared" si="12"/>
+        <v>14428.8725</v>
+      </c>
+      <c r="D68" s="5">
+        <f t="shared" si="12"/>
+        <v>20022.7475</v>
+      </c>
+      <c r="E68" s="5">
+        <f t="shared" si="12"/>
+        <v>12879.358</v>
+      </c>
+      <c r="F68" s="5">
+        <f t="shared" si="12"/>
+        <v>10576.564</v>
+      </c>
+      <c r="G68" s="5">
+        <f t="shared" si="12"/>
+        <v>14472.008</v>
+      </c>
+      <c r="H68" s="5">
+        <f t="shared" si="12"/>
+        <v>17632.932</v>
+      </c>
+      <c r="I68" s="5">
+        <f t="shared" si="12"/>
+        <v>16201.158</v>
+      </c>
+      <c r="J68" s="5">
+        <f t="shared" si="12"/>
+        <v>10893.582</v>
+      </c>
+      <c r="K68" s="5">
+        <f t="shared" si="12"/>
+        <v>10478.64</v>
+      </c>
+      <c r="L68" s="5">
+        <f t="shared" si="12"/>
+        <v>7528.564</v>
+      </c>
+      <c r="M68" s="5">
+        <f t="shared" si="12"/>
+        <v>6484.368</v>
+      </c>
+      <c r="N68" s="5">
+        <f t="shared" si="12"/>
+        <v>10965.62667</v>
+      </c>
+      <c r="O68" s="5">
+        <f t="shared" si="12"/>
+        <v>7259.26</v>
+      </c>
+      <c r="P68" s="5">
+        <f t="shared" si="12"/>
+        <v>6149.781429</v>
+      </c>
+      <c r="Q68" s="5">
+        <f t="shared" si="12"/>
+        <v>10070.49286</v>
+      </c>
+      <c r="R68" s="5">
+        <f t="shared" si="12"/>
+        <v>13479.04857</v>
+      </c>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="5">
+        <f>average(N68:Y68)</f>
+        <v>9584.841905</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" s="11">
+        <f t="shared" ref="B69:S69" si="13">average(B53,B45,B37,B29,B21,B13,B5)</f>
+        <v>0.3444333333</v>
+      </c>
+      <c r="C69" s="11">
         <f t="shared" si="13"/>
-        <v>14428.8725</v>
-      </c>
-      <c r="D68" s="6">
+        <v>0.309525</v>
+      </c>
+      <c r="D69" s="11">
         <f t="shared" si="13"/>
-        <v>20022.7475</v>
-      </c>
-      <c r="E68" s="6">
+        <v>0.42125</v>
+      </c>
+      <c r="E69" s="11">
         <f t="shared" si="13"/>
-        <v>12879.358</v>
-      </c>
-      <c r="F68" s="6">
+        <v>0.42478</v>
+      </c>
+      <c r="F69" s="11">
         <f t="shared" si="13"/>
-        <v>10576.564</v>
-      </c>
-      <c r="G68" s="6">
+        <v>0.40488</v>
+      </c>
+      <c r="G69" s="11">
         <f t="shared" si="13"/>
-        <v>14472.008</v>
-      </c>
-      <c r="H68" s="6">
+        <v>0.45414</v>
+      </c>
+      <c r="H69" s="11">
         <f t="shared" si="13"/>
-        <v>17632.932</v>
-      </c>
-      <c r="I68" s="6">
+        <v>0.40556</v>
+      </c>
+      <c r="I69" s="11">
         <f t="shared" si="13"/>
-        <v>16201.158</v>
-      </c>
-      <c r="J68" s="6">
+        <v>0.31688</v>
+      </c>
+      <c r="J69" s="11">
         <f t="shared" si="13"/>
-        <v>10893.582</v>
-      </c>
-      <c r="K68" s="6">
+        <v>0.41248</v>
+      </c>
+      <c r="K69" s="11">
         <f t="shared" si="13"/>
-        <v>10478.64</v>
-      </c>
-      <c r="L68" s="6">
+        <v>0.29162</v>
+      </c>
+      <c r="L69" s="11">
         <f t="shared" si="13"/>
-        <v>7528.564</v>
-      </c>
-      <c r="M68" s="6">
+        <v>0.35694</v>
+      </c>
+      <c r="M69" s="11">
         <f t="shared" si="13"/>
-        <v>6484.368</v>
-      </c>
-      <c r="N68" s="6">
+        <v>0.3687333333</v>
+      </c>
+      <c r="N69" s="11">
         <f t="shared" si="13"/>
-        <v>10965.62667</v>
-      </c>
-      <c r="O68" s="6">
+        <v>0.26642</v>
+      </c>
+      <c r="O69" s="11">
         <f t="shared" si="13"/>
-        <v>7259.26</v>
-      </c>
-      <c r="P68" s="6">
+        <v>0.2291666667</v>
+      </c>
+      <c r="P69" s="11">
         <f t="shared" si="13"/>
-        <v>6149.781429</v>
-      </c>
-      <c r="Q68" s="6">
+        <v>0.3634</v>
+      </c>
+      <c r="Q69" s="11">
         <f t="shared" si="13"/>
-        <v>10070.49286</v>
-      </c>
-      <c r="R68" s="6">
+        <v>0.2847571429</v>
+      </c>
+      <c r="R69" s="11">
         <f t="shared" si="13"/>
-        <v>13479.04857</v>
-      </c>
-      <c r="S68" s="4" t="str">
+        <v>0.15246</v>
+      </c>
+      <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T68" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U68" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V68" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W68" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X68" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y68" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z68" s="6" t="str">
-        <f>average(N68:Y68)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" s="14">
-        <f t="shared" ref="B69:R69" si="14">average(B53,B45,B37,B29,B21,B13,B5)</f>
-        <v>0.3444333333</v>
-      </c>
-      <c r="C69" s="14">
+        <v>0.1382333333</v>
+      </c>
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="11">
+        <f>average(R69:Y69)</f>
+        <v>0.1453466667</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="11">
+        <f t="shared" ref="B70:S70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <v>0.50445</v>
+      </c>
+      <c r="C70" s="11">
         <f t="shared" si="14"/>
-        <v>0.309525</v>
-      </c>
-      <c r="D69" s="14">
+        <v>0.366525</v>
+      </c>
+      <c r="D70" s="11">
         <f t="shared" si="14"/>
-        <v>0.42125</v>
-      </c>
-      <c r="E69" s="14">
+        <v>0.30455</v>
+      </c>
+      <c r="E70" s="11">
         <f t="shared" si="14"/>
-        <v>0.42478</v>
-      </c>
-      <c r="F69" s="14">
+        <v>0.38494</v>
+      </c>
+      <c r="F70" s="11">
         <f t="shared" si="14"/>
-        <v>0.40488</v>
-      </c>
-      <c r="G69" s="14">
+        <v>0.40984</v>
+      </c>
+      <c r="G70" s="11">
         <f t="shared" si="14"/>
-        <v>0.45414</v>
-      </c>
-      <c r="H69" s="14">
+        <v>0.4393</v>
+      </c>
+      <c r="H70" s="11">
         <f t="shared" si="14"/>
-        <v>0.40556</v>
-      </c>
-      <c r="I69" s="14">
+        <v>0.42082</v>
+      </c>
+      <c r="I70" s="11">
         <f t="shared" si="14"/>
-        <v>0.31688</v>
-      </c>
-      <c r="J69" s="14">
+        <v>0.4131</v>
+      </c>
+      <c r="J70" s="11">
         <f t="shared" si="14"/>
-        <v>0.41248</v>
-      </c>
-      <c r="K69" s="14">
+        <v>0.3999</v>
+      </c>
+      <c r="K70" s="11">
         <f t="shared" si="14"/>
-        <v>0.29162</v>
-      </c>
-      <c r="L69" s="14">
+        <v>0.38592</v>
+      </c>
+      <c r="L70" s="11">
         <f t="shared" si="14"/>
-        <v>0.35694</v>
-      </c>
-      <c r="M69" s="14">
+        <v>0.33754</v>
+      </c>
+      <c r="M70" s="11">
         <f t="shared" si="14"/>
-        <v>0.3687333333</v>
-      </c>
-      <c r="N69" s="14">
+        <v>0.34014</v>
+      </c>
+      <c r="N70" s="11">
         <f t="shared" si="14"/>
-        <v>0.26642</v>
-      </c>
-      <c r="O69" s="14">
+        <v>0.30044</v>
+      </c>
+      <c r="O70" s="11">
         <f t="shared" si="14"/>
-        <v>0.2291666667</v>
-      </c>
-      <c r="P69" s="14">
+        <v>0.30184</v>
+      </c>
+      <c r="P70" s="11">
         <f t="shared" si="14"/>
-        <v>0.3634</v>
-      </c>
-      <c r="Q69" s="14">
+        <v>0.2368833333</v>
+      </c>
+      <c r="Q70" s="11">
         <f t="shared" si="14"/>
-        <v>0.2847571429</v>
-      </c>
-      <c r="R69" s="14">
+        <v>0.3044714286</v>
+      </c>
+      <c r="R70" s="11">
         <f t="shared" si="14"/>
-        <v>0.15246</v>
-      </c>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4" t="str">
-        <f t="shared" ref="T69:Y69" si="15">AVERAGE(T62,T54,T46,T38,T30,T22,T14,T6)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U69" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V69" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W69" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X69" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y69" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z69" s="4" t="str">
-        <f>average(R69:Y69)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B70" s="14">
-        <f t="shared" ref="B70:R70" si="16">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
-        <v>0.50445</v>
-      </c>
-      <c r="C70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.366525</v>
-      </c>
-      <c r="D70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.30455</v>
-      </c>
-      <c r="E70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.38494</v>
-      </c>
-      <c r="F70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.40984</v>
-      </c>
-      <c r="G70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.4393</v>
-      </c>
-      <c r="H70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.42082</v>
-      </c>
-      <c r="I70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.4131</v>
-      </c>
-      <c r="J70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.3999</v>
-      </c>
-      <c r="K70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.38592</v>
-      </c>
-      <c r="L70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.33754</v>
-      </c>
-      <c r="M70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.34014</v>
-      </c>
-      <c r="N70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.30044</v>
-      </c>
-      <c r="O70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.30184</v>
-      </c>
-      <c r="P70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.2368833333</v>
-      </c>
-      <c r="Q70" s="14">
-        <f t="shared" si="16"/>
-        <v>0.3044714286</v>
-      </c>
-      <c r="R70" s="14">
-        <f t="shared" si="16"/>
         <v>0.2830428571</v>
+      </c>
+      <c r="S70" s="11">
+        <f t="shared" si="14"/>
+        <v>0.2241285714</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3588,30 +3508,30 @@
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="1"/>
-      <c r="S79" s="14"/>
+      <c r="S79" s="11"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="1"/>
-      <c r="S80" s="14"/>
+      <c r="S80" s="11"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="1"/>
-      <c r="S81" s="14"/>
+      <c r="S81" s="11"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="1"/>
-      <c r="S82" s="14"/>
+      <c r="S82" s="11"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="1"/>
-      <c r="S83" s="14"/>
+      <c r="S83" s="11"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="1"/>
-      <c r="S84" s="14"/>
+      <c r="S84" s="11"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="S85" s="14"/>
+      <c r="S85" s="11"/>
     </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
@@ -3637,71 +3557,71 @@
     <row r="107" ht="15.75" customHeight="1"/>
     <row r="108" ht="15.75" customHeight="1"/>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="14" t="str">
-        <f t="shared" ref="C109:R109" si="17">average(C79:C84)</f>
+      <c r="C109" s="11" t="str">
+        <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="D109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="E109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="F109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="G109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="H109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="I109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="J109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="K109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="L109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="M109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="N109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="O109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="P109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="Q109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R109" s="14" t="str">
-        <f t="shared" si="17"/>
+      <c r="R109" s="11" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4596,15 +4516,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
-    <row r="1004" ht="15.75" customHeight="1"/>
-    <row r="1005" ht="15.75" customHeight="1"/>
-    <row r="1006" ht="15.75" customHeight="1"/>
-    <row r="1007" ht="15.75" customHeight="1"/>
-    <row r="1008" ht="15.75" customHeight="1"/>
-    <row r="1009" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -697,7 +697,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.3333</v>
+        <v>0.04</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -707,7 +707,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.2846333333</v>
+        <v>0.23575</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -766,7 +766,7 @@
         <v>0.3426</v>
       </c>
       <c r="S6" s="12">
-        <v>0.2673</v>
+        <v>0.2549</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -776,7 +776,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2694666667</v>
+        <v>0.2674</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1155,7 +1155,7 @@
         <v>0.2711</v>
       </c>
       <c r="S14" s="12">
-        <v>0.2044</v>
+        <v>0.2031</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="15"/>
@@ -1163,7 +1163,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.23775</v>
+        <v>0.2371</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1528,7 +1528,7 @@
         <v>0.232</v>
       </c>
       <c r="S22" s="12">
-        <v>0.181</v>
+        <v>0.1881</v>
       </c>
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
@@ -1538,7 +1538,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.2065</v>
+        <v>0.21005</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1916,7 +1916,7 @@
         <v>0.3297</v>
       </c>
       <c r="S30" s="12">
-        <v>0.2759</v>
+        <v>0.2778</v>
       </c>
       <c r="T30" s="16"/>
       <c r="U30" s="11"/>
@@ -1926,7 +1926,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.3028</v>
+        <v>0.30375</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2241,7 +2241,7 @@
         <v>0.0606</v>
       </c>
       <c r="S37" s="12">
-        <v>0.3333</v>
+        <v>0.2</v>
       </c>
       <c r="T37" s="11"/>
       <c r="U37" s="11"/>
@@ -2307,7 +2307,7 @@
         <v>0.2432</v>
       </c>
       <c r="S38" s="12">
-        <v>0.2024</v>
+        <v>0.1923</v>
       </c>
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
@@ -2317,7 +2317,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2228</v>
+        <v>0.21775</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2529,7 +2529,7 @@
         <v>0.2667</v>
       </c>
       <c r="S46" s="12">
-        <v>0.2157</v>
+        <v>0.2062</v>
       </c>
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
@@ -2539,7 +2539,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2412</v>
+        <v>0.23645</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2713,7 +2713,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0333</v>
+        <v>0.0294</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2749,7 +2749,7 @@
         <v>0.296</v>
       </c>
       <c r="S54" s="12">
-        <v>0.2222</v>
+        <v>0.2114</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
@@ -2759,7 +2759,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2591</v>
+        <v>0.2537</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.1382333333</v>
+        <v>0.06648333333</v>
       </c>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
@@ -3418,7 +3418,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.1453466667</v>
+        <v>0.1094716667</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S70" s="11">
         <f t="shared" si="14"/>
-        <v>0.2241285714</v>
+        <v>0.2191142857</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -169,6 +169,9 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -697,7 +700,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.04</v>
+        <v>0.0385</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -707,7 +710,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.23575</v>
+        <v>0.2355</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -766,7 +769,7 @@
         <v>0.3426</v>
       </c>
       <c r="S6" s="12">
-        <v>0.2549</v>
+        <v>0.2647</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -776,7 +779,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2674</v>
+        <v>0.2690333333</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1092,7 +1095,7 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="12">
+      <c r="S13" s="11">
         <v>0.0526</v>
       </c>
       <c r="T13" s="14"/>
@@ -1154,8 +1157,8 @@
       <c r="R14" s="11">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="12">
-        <v>0.2031</v>
+      <c r="S14" s="16">
+        <v>22.66</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="15"/>
@@ -1163,12 +1166,12 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2371</v>
+        <v>11.46555</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="S15" s="11"/>
-      <c r="T15" s="16"/>
+      <c r="T15" s="17"/>
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
@@ -1469,7 +1472,7 @@
         <v>0.22</v>
       </c>
       <c r="R21" s="11"/>
-      <c r="S21" s="12"/>
+      <c r="S21" s="11"/>
       <c r="T21" s="11"/>
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
@@ -1528,7 +1531,7 @@
         <v>0.232</v>
       </c>
       <c r="S22" s="12">
-        <v>0.1881</v>
+        <v>0.1765</v>
       </c>
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
@@ -1538,7 +1541,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.21005</v>
+        <v>0.20425</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1851,10 +1854,10 @@
         <v>0.2759</v>
       </c>
       <c r="R29" s="11"/>
-      <c r="S29" s="12">
+      <c r="S29" s="11">
         <v>0.0769</v>
       </c>
-      <c r="T29" s="16"/>
+      <c r="T29" s="17"/>
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
@@ -1916,9 +1919,9 @@
         <v>0.3297</v>
       </c>
       <c r="S30" s="12">
-        <v>0.2778</v>
-      </c>
-      <c r="T30" s="16"/>
+        <v>0.2549</v>
+      </c>
+      <c r="T30" s="17"/>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
@@ -1926,7 +1929,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.30375</v>
+        <v>0.2923</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2240,7 +2243,7 @@
       <c r="R37" s="11">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="12">
+      <c r="S37" s="11">
         <v>0.2</v>
       </c>
       <c r="T37" s="11"/>
@@ -2306,7 +2309,7 @@
       <c r="R38" s="11">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="12">
+      <c r="S38" s="11">
         <v>0.1923</v>
       </c>
       <c r="T38" s="11"/>
@@ -2472,7 +2475,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="17"/>
+      <c r="I45" s="18"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2490,7 +2493,7 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="12">
+      <c r="S45" s="11">
         <v>0.0</v>
       </c>
       <c r="T45" s="11"/>
@@ -2529,7 +2532,7 @@
         <v>0.2667</v>
       </c>
       <c r="S46" s="12">
-        <v>0.2062</v>
+        <v>0.1979</v>
       </c>
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
@@ -2539,7 +2542,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.23645</v>
+        <v>0.2323</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2713,7 +2716,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0294</v>
+        <v>0.0588</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2749,7 +2752,7 @@
         <v>0.296</v>
       </c>
       <c r="S54" s="12">
-        <v>0.2114</v>
+        <v>0.2131</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
@@ -2759,7 +2762,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2537</v>
+        <v>0.25455</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3070,8 +3073,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="18"/>
-      <c r="T65" s="18"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3170,71 +3173,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="20">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="19">
+      <c r="C67" s="20">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="20">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="19">
+      <c r="F67" s="20">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="19">
+      <c r="G67" s="20">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="19">
+      <c r="H67" s="20">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="19">
+      <c r="I67" s="20">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="19">
+      <c r="J67" s="20">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="19">
+      <c r="K67" s="20">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="20">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="19">
+      <c r="M67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="19">
+      <c r="N67" s="20">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="19">
+      <c r="O67" s="20">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="19">
+      <c r="P67" s="20">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="19">
+      <c r="Q67" s="20">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="19">
+      <c r="R67" s="20">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3245,7 +3248,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="19">
+      <c r="Z67" s="20">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3408,7 +3411,7 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.06648333333</v>
+        <v>0.07113333333</v>
       </c>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
@@ -3418,7 +3421,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.1094716667</v>
+        <v>0.1117966667</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3495,7 +3498,7 @@
       </c>
       <c r="S70" s="11">
         <f t="shared" si="14"/>
-        <v>0.2191142857</v>
+        <v>3.422771429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -169,9 +169,6 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -769,7 +766,7 @@
         <v>0.3426</v>
       </c>
       <c r="S6" s="12">
-        <v>0.2647</v>
+        <v>0.2772</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -779,7 +776,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2690333333</v>
+        <v>0.2711166667</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1095,8 +1092,8 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="11">
-        <v>0.0526</v>
+      <c r="S13" s="12">
+        <v>0.0476</v>
       </c>
       <c r="T13" s="14"/>
       <c r="W13" s="15"/>
@@ -1157,8 +1154,8 @@
       <c r="R14" s="11">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="16">
-        <v>22.66</v>
+      <c r="S14" s="12">
+        <v>0.2403</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="15"/>
@@ -1166,12 +1163,12 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>11.46555</v>
+        <v>0.2557</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="S15" s="11"/>
-      <c r="T15" s="17"/>
+      <c r="T15" s="16"/>
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
@@ -1531,7 +1528,7 @@
         <v>0.232</v>
       </c>
       <c r="S22" s="12">
-        <v>0.1765</v>
+        <v>0.1818</v>
       </c>
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
@@ -1541,7 +1538,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.20425</v>
+        <v>0.2069</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1854,10 +1851,10 @@
         <v>0.2759</v>
       </c>
       <c r="R29" s="11"/>
-      <c r="S29" s="11">
-        <v>0.0769</v>
-      </c>
-      <c r="T29" s="17"/>
+      <c r="S29" s="12">
+        <v>0.0714</v>
+      </c>
+      <c r="T29" s="16"/>
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
@@ -1919,9 +1916,9 @@
         <v>0.3297</v>
       </c>
       <c r="S30" s="12">
-        <v>0.2549</v>
-      </c>
-      <c r="T30" s="17"/>
+        <v>0.24</v>
+      </c>
+      <c r="T30" s="16"/>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
@@ -1929,7 +1926,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2923</v>
+        <v>0.28485</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2309,8 +2306,8 @@
       <c r="R38" s="11">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="11">
-        <v>0.1923</v>
+      <c r="S38" s="12">
+        <v>0.1948</v>
       </c>
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
@@ -2320,7 +2317,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.21775</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2475,7 +2472,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="18"/>
+      <c r="I45" s="17"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2493,9 +2490,7 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="11">
-        <v>0.0</v>
-      </c>
+      <c r="S45" s="11"/>
       <c r="T45" s="11"/>
       <c r="U45" s="11"/>
       <c r="V45" s="11"/>
@@ -2532,7 +2527,7 @@
         <v>0.2667</v>
       </c>
       <c r="S46" s="12">
-        <v>0.1979</v>
+        <v>0.1957</v>
       </c>
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
@@ -2542,7 +2537,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2323</v>
+        <v>0.2312</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2716,7 +2711,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0588</v>
+        <v>0.0789</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2752,7 +2747,7 @@
         <v>0.296</v>
       </c>
       <c r="S54" s="12">
-        <v>0.2131</v>
+        <v>0.2114</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
@@ -2762,7 +2757,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.25455</v>
+        <v>0.2537</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3073,8 +3068,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="19"/>
-      <c r="T65" s="19"/>
+      <c r="S65" s="18"/>
+      <c r="T65" s="18"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3173,71 +3168,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="19">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="20">
+      <c r="C67" s="19">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="19">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="19">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="19">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="20">
+      <c r="G67" s="19">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="20">
+      <c r="H67" s="19">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="20">
+      <c r="I67" s="19">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="20">
+      <c r="J67" s="19">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="20">
+      <c r="K67" s="19">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="20">
+      <c r="L67" s="19">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="20">
+      <c r="M67" s="19">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="20">
+      <c r="N67" s="19">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="20">
+      <c r="O67" s="19">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="20">
+      <c r="P67" s="19">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="20">
+      <c r="Q67" s="19">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="20">
+      <c r="R67" s="19">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3248,7 +3243,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="20">
+      <c r="Z67" s="19">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3411,7 +3406,7 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.07113333333</v>
+        <v>0.08728</v>
       </c>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
@@ -3421,7 +3416,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.1117966667</v>
+        <v>0.11987</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3498,7 +3493,7 @@
       </c>
       <c r="S70" s="11">
         <f t="shared" si="14"/>
-        <v>3.422771429</v>
+        <v>0.2201714286</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -697,7 +697,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.0385</v>
+        <v>0.037</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -707,7 +707,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.2355</v>
+        <v>0.23525</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -766,7 +766,7 @@
         <v>0.3426</v>
       </c>
       <c r="S6" s="12">
-        <v>0.2772</v>
+        <v>0.2745</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -776,7 +776,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2711166667</v>
+        <v>0.2706666667</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1093,7 +1093,7 @@
         <v>0.0513</v>
       </c>
       <c r="S13" s="12">
-        <v>0.0476</v>
+        <v>0.0455</v>
       </c>
       <c r="T13" s="14"/>
       <c r="W13" s="15"/>
@@ -1155,7 +1155,7 @@
         <v>0.2711</v>
       </c>
       <c r="S14" s="12">
-        <v>0.2403</v>
+        <v>0.2339</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="15"/>
@@ -1163,7 +1163,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2557</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1528,7 +1528,7 @@
         <v>0.232</v>
       </c>
       <c r="S22" s="12">
-        <v>0.1818</v>
+        <v>0.1443</v>
       </c>
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
@@ -1538,7 +1538,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.2069</v>
+        <v>0.18815</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="R29" s="11"/>
       <c r="S29" s="12">
-        <v>0.0714</v>
+        <v>0.0625</v>
       </c>
       <c r="T29" s="16"/>
       <c r="U29" s="11"/>
@@ -1916,7 +1916,7 @@
         <v>0.3297</v>
       </c>
       <c r="S30" s="12">
-        <v>0.24</v>
+        <v>0.2308</v>
       </c>
       <c r="T30" s="16"/>
       <c r="U30" s="11"/>
@@ -1926,7 +1926,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.28485</v>
+        <v>0.28025</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2240,8 +2240,8 @@
       <c r="R37" s="11">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="11">
-        <v>0.2</v>
+      <c r="S37" s="12">
+        <v>0.1429</v>
       </c>
       <c r="T37" s="11"/>
       <c r="U37" s="11"/>
@@ -2307,7 +2307,7 @@
         <v>0.2432</v>
       </c>
       <c r="S38" s="12">
-        <v>0.1948</v>
+        <v>0.1974</v>
       </c>
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
@@ -2317,7 +2317,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.219</v>
+        <v>0.2203</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2527,7 +2527,7 @@
         <v>0.2667</v>
       </c>
       <c r="S46" s="12">
-        <v>0.1957</v>
+        <v>0.1705</v>
       </c>
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
@@ -2537,7 +2537,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2312</v>
+        <v>0.2186</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2711,7 +2711,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0789</v>
+        <v>0.0698</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2747,7 +2747,7 @@
         <v>0.296</v>
       </c>
       <c r="S54" s="12">
-        <v>0.2114</v>
+        <v>0.192</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
@@ -2757,7 +2757,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2537</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.08728</v>
+        <v>0.07154</v>
       </c>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
@@ -3416,7 +3416,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.11987</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="S70" s="11">
         <f t="shared" si="14"/>
-        <v>0.2201714286</v>
+        <v>0.2062</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -697,7 +697,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.037</v>
+        <v>0.0968</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -707,7 +707,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.23525</v>
+        <v>0.2452166667</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -765,10 +765,12 @@
       <c r="R6" s="11">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="11">
         <v>0.2745</v>
       </c>
-      <c r="T6" s="11"/>
+      <c r="T6" s="12">
+        <v>0.2551</v>
+      </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
@@ -776,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2706666667</v>
+        <v>0.2684428571</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1093,7 +1095,7 @@
         <v>0.0513</v>
       </c>
       <c r="S13" s="12">
-        <v>0.0455</v>
+        <v>0.0435</v>
       </c>
       <c r="T13" s="14"/>
       <c r="W13" s="15"/>
@@ -1154,16 +1156,20 @@
       <c r="R14" s="11">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="12">
+      <c r="S14" s="11">
         <v>0.2339</v>
       </c>
-      <c r="T14" s="14"/>
-      <c r="W14" s="15"/>
+      <c r="T14" s="12">
+        <v>0.2393</v>
+      </c>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2525</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1527,10 +1533,12 @@
       <c r="R22" s="11">
         <v>0.232</v>
       </c>
-      <c r="S22" s="12">
+      <c r="S22" s="11">
         <v>0.1443</v>
       </c>
-      <c r="T22" s="11"/>
+      <c r="T22" s="12">
+        <v>0.1505</v>
+      </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
@@ -1538,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.18815</v>
+        <v>0.1756</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1852,7 +1860,7 @@
       </c>
       <c r="R29" s="11"/>
       <c r="S29" s="12">
-        <v>0.0625</v>
+        <v>0.0588</v>
       </c>
       <c r="T29" s="16"/>
       <c r="U29" s="11"/>
@@ -1915,10 +1923,12 @@
       <c r="R30" s="11">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="12">
+      <c r="S30" s="11">
         <v>0.2308</v>
       </c>
-      <c r="T30" s="16"/>
+      <c r="T30" s="12">
+        <v>0.2</v>
+      </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
@@ -1926,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.28025</v>
+        <v>0.2535</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2241,7 +2251,7 @@
         <v>0.0606</v>
       </c>
       <c r="S37" s="12">
-        <v>0.1429</v>
+        <v>0.1111</v>
       </c>
       <c r="T37" s="11"/>
       <c r="U37" s="11"/>
@@ -2306,10 +2316,12 @@
       <c r="R38" s="11">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="12">
+      <c r="S38" s="11">
         <v>0.1974</v>
       </c>
-      <c r="T38" s="11"/>
+      <c r="T38" s="12">
+        <v>0.1757</v>
+      </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
       <c r="W38" s="11"/>
@@ -2317,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2203</v>
+        <v>0.2054333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2526,10 +2538,12 @@
       <c r="R46" s="11">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="12">
+      <c r="S46" s="11">
         <v>0.1705</v>
       </c>
-      <c r="T46" s="11"/>
+      <c r="T46" s="12">
+        <v>0.1548</v>
+      </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
       <c r="W46" s="11"/>
@@ -2537,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2186</v>
+        <v>0.1973333333</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2711,7 +2725,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0698</v>
+        <v>0.093</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2746,10 +2760,12 @@
       <c r="R54" s="11">
         <v>0.296</v>
       </c>
-      <c r="S54" s="12">
+      <c r="S54" s="11">
         <v>0.192</v>
       </c>
-      <c r="T54" s="11"/>
+      <c r="T54" s="12">
+        <v>0.2016</v>
+      </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
       <c r="W54" s="11"/>
@@ -2757,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.244</v>
+        <v>0.2298666667</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3406,9 +3422,9 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.07154</v>
-      </c>
-      <c r="T69" s="3"/>
+        <v>0.08064</v>
+      </c>
+      <c r="T69" s="11"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
@@ -3416,7 +3432,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.112</v>
+        <v>0.11655</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3424,7 +3440,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="11">
-        <f t="shared" ref="B70:S70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
       <c r="C70" s="11">
@@ -3494,6 +3510,10 @@
       <c r="S70" s="11">
         <f t="shared" si="14"/>
         <v>0.2062</v>
+      </c>
+      <c r="T70" s="11">
+        <f t="shared" si="14"/>
+        <v>0.1967142857</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.2551</v>
+        <v>0.2449</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2684428571</v>
+        <v>0.2669857143</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2393</v>
+        <v>0.2261</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2481</v>
+        <v>0.2437</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1537,7 +1537,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="12">
-        <v>0.1505</v>
+        <v>0.1264</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
@@ -1546,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.1756</v>
+        <v>0.1675666667</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.2</v>
+        <v>0.1837</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2535</v>
+        <v>0.2480666667</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1757</v>
+        <v>0.1644</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2054333333</v>
+        <v>0.2016666667</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1548</v>
+        <v>0.1429</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1973333333</v>
+        <v>0.1933666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1967142857</v>
+        <v>0.1842857143</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.2449</v>
+        <v>0.2474</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2669857143</v>
+        <v>0.2673428571</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2261</v>
+        <v>0.2155</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2437</v>
+        <v>0.2401666667</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.1837</v>
+        <v>0.1923</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2480666667</v>
+        <v>0.2509333333</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1644</v>
+        <v>0.1739</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2016666667</v>
+        <v>0.2048333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1429</v>
+        <v>0.1375</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1933666667</v>
+        <v>0.1915666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1842857143</v>
+        <v>0.1849428571</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.2474</v>
+        <v>0.2143</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2673428571</v>
+        <v>0.2626142857</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2155</v>
+        <v>0.2047</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2401666667</v>
+        <v>0.2365666667</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1537,7 +1537,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="12">
-        <v>0.1264</v>
+        <v>0.129</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
@@ -1546,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.1675666667</v>
+        <v>0.1684333333</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.1923</v>
+        <v>0.1887</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2509333333</v>
+        <v>0.2497333333</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1739</v>
+        <v>0.1778</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2048333333</v>
+        <v>0.2061333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1375</v>
+        <v>0.1333</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1915666667</v>
+        <v>0.1901666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2764,7 +2764,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="12">
-        <v>0.2016</v>
+        <v>0.2</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
@@ -2773,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2298666667</v>
+        <v>0.2293333333</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1849428571</v>
+        <v>0.1782571429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.2143</v>
+        <v>0.1895</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2626142857</v>
+        <v>0.2590714286</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2047</v>
+        <v>0.2063</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2365666667</v>
+        <v>0.2371</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1537,7 +1537,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="12">
-        <v>0.129</v>
+        <v>0.1319</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
@@ -1546,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.1684333333</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1778</v>
+        <v>0.1591</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2061333333</v>
+        <v>0.1999</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1333</v>
+        <v>0.1233</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1901666667</v>
+        <v>0.1868333333</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2764,7 +2764,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="12">
-        <v>0.2</v>
+        <v>0.2017</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
@@ -2773,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2293333333</v>
+        <v>0.2299</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1782571429</v>
+        <v>0.1715</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.1895</v>
+        <v>0.1978</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2590714286</v>
+        <v>0.2602571429</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2063</v>
+        <v>0.1641</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2371</v>
+        <v>0.2230333333</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1537,7 +1537,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="12">
-        <v>0.1319</v>
+        <v>0.1034</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
@@ -1546,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.1694</v>
+        <v>0.1599</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.1887</v>
+        <v>0.16</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2497333333</v>
+        <v>0.2401666667</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1591</v>
+        <v>0.1</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.1999</v>
+        <v>0.1802</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1233</v>
+        <v>0.1194</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1868333333</v>
+        <v>0.1855333333</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2764,7 +2764,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="12">
-        <v>0.2017</v>
+        <v>0.1951</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
@@ -2773,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2299</v>
+        <v>0.2277</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1715</v>
+        <v>0.1485428571</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.1978</v>
+        <v>0.1932</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2602571429</v>
+        <v>0.2596</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.1641</v>
+        <v>0.1508</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2230333333</v>
+        <v>0.2186</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.16</v>
+        <v>0.1875</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2401666667</v>
+        <v>0.2493333333</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1</v>
+        <v>0.1053</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.1802</v>
+        <v>0.1819666667</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1194</v>
+        <v>0.127</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1855333333</v>
+        <v>0.1880666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2764,7 +2764,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="12">
-        <v>0.1951</v>
+        <v>0.1935</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
@@ -2773,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2277</v>
+        <v>0.2271666667</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1485428571</v>
+        <v>0.1515285714</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -158,6 +158,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -699,7 +702,7 @@
       <c r="S5" s="10">
         <v>0.0968</v>
       </c>
-      <c r="T5" s="9"/>
+      <c r="T5" s="11"/>
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -714,71 +717,71 @@
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="12">
         <v>0.5714</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <v>0.4167</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="12">
         <v>0.3182</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="12">
         <v>0.3333</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <v>0.3429</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="12">
         <v>0.4348</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="12">
         <v>0.4468</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="12">
         <v>0.3462</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="12">
         <v>0.2456</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="12">
         <v>0.2203</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="12">
         <v>0.2537</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="12">
         <v>0.2593</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="12">
         <v>0.2368</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="12">
         <v>0.2308</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="12">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6" s="12">
         <v>0.3393</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="12">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="11">
+      <c r="S6" s="12">
         <v>0.2745</v>
       </c>
-      <c r="T6" s="12">
-        <v>0.1932</v>
-      </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="11">
+      <c r="T6" s="13">
+        <v>0.1867</v>
+      </c>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2596</v>
+        <v>0.2586714286</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -916,7 +919,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="13"/>
+      <c r="W10" s="14"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -975,7 +978,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="13"/>
+      <c r="W11" s="14"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1033,7 +1036,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="13"/>
+      <c r="W12" s="14"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1094,103 +1097,103 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="12">
+      <c r="S13" s="13">
         <v>0.0435</v>
       </c>
-      <c r="T13" s="14"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="11"/>
-      <c r="Z13" s="11"/>
+      <c r="T13" s="15"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12">
         <v>0.5161</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="12">
         <v>0.3333</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="12">
         <v>0.34</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="12">
         <v>0.3521</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="12">
         <v>0.4125</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="12">
         <v>0.4321</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="12">
         <v>0.369</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="12">
         <v>0.3194</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="12">
         <v>0.2969</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="12">
         <v>0.32</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="12">
         <v>0.3205</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="12">
         <v>0.3571</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="12">
         <v>0.449</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="12">
         <v>0.4182</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="Q14" s="12">
         <v>0.3269</v>
       </c>
-      <c r="R14" s="11">
+      <c r="R14" s="12">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="11">
+      <c r="S14" s="12">
         <v>0.2339</v>
       </c>
-      <c r="T14" s="12">
-        <v>0.1508</v>
-      </c>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="11">
+      <c r="T14" s="13">
+        <v>0.099</v>
+      </c>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.2186</v>
+        <v>0.2013333333</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="S15" s="11"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="11"/>
-      <c r="Z16" s="11"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
@@ -1474,79 +1477,79 @@
       <c r="Q21" s="8">
         <v>0.22</v>
       </c>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="11"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="11"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
       <c r="Z21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12">
         <v>0.5</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="12">
         <v>0.5625</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="12">
         <v>0.5714</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="12">
         <v>0.4815</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="12">
         <v>0.4634</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="12">
         <v>0.4898</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="12">
         <v>0.463</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="12">
         <v>0.377</v>
       </c>
-      <c r="M22" s="11">
+      <c r="M22" s="12">
         <v>0.3387</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="12">
         <v>0.3265</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="12">
         <v>0.3056</v>
       </c>
-      <c r="P22" s="11">
+      <c r="P22" s="12">
         <v>0.2075</v>
       </c>
-      <c r="Q22" s="11">
+      <c r="Q22" s="12">
         <v>0.2615</v>
       </c>
-      <c r="R22" s="11">
+      <c r="R22" s="12">
         <v>0.232</v>
       </c>
-      <c r="S22" s="11">
+      <c r="S22" s="12">
         <v>0.1443</v>
       </c>
-      <c r="T22" s="12">
-        <v>0.1034</v>
-      </c>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="11">
+      <c r="T22" s="13">
+        <v>0.0575</v>
+      </c>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1599</v>
+        <v>0.1446</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1743,7 +1746,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="13"/>
+      <c r="W27" s="14"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1801,8 +1804,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="14"/>
-      <c r="W28" s="13"/>
+      <c r="T28" s="15"/>
+      <c r="W28" s="14"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1858,85 +1861,85 @@
       <c r="Q29" s="8">
         <v>0.2759</v>
       </c>
-      <c r="R29" s="11"/>
-      <c r="S29" s="12">
+      <c r="R29" s="12"/>
+      <c r="S29" s="13">
         <v>0.0588</v>
       </c>
-      <c r="T29" s="16"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="11"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="11"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
       <c r="Z29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12">
         <v>0.1333</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="12">
         <v>0.1667</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="12">
         <v>0.3514</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="12">
         <v>0.375</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="12">
         <v>0.3778</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="12">
         <v>0.3226</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="12">
         <v>0.4359</v>
       </c>
-      <c r="J30" s="11">
+      <c r="J30" s="12">
         <v>0.4286</v>
       </c>
-      <c r="K30" s="11">
+      <c r="K30" s="12">
         <v>0.4366</v>
       </c>
-      <c r="L30" s="11">
+      <c r="L30" s="12">
         <v>0.3457</v>
       </c>
-      <c r="M30" s="11">
+      <c r="M30" s="12">
         <v>0.3222</v>
       </c>
-      <c r="N30" s="11">
+      <c r="N30" s="12">
         <v>0.2568</v>
       </c>
-      <c r="O30" s="11">
+      <c r="O30" s="12">
         <v>0.1905</v>
       </c>
-      <c r="P30" s="11">
+      <c r="P30" s="12">
         <v>0.2281</v>
       </c>
-      <c r="Q30" s="11">
+      <c r="Q30" s="12">
         <v>0.3243</v>
       </c>
-      <c r="R30" s="11">
+      <c r="R30" s="12">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="11">
+      <c r="S30" s="12">
         <v>0.2308</v>
       </c>
-      <c r="T30" s="12">
-        <v>0.1875</v>
-      </c>
-      <c r="U30" s="11"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="11"/>
-      <c r="Z30" s="11">
+      <c r="T30" s="13">
+        <v>0.1591</v>
+      </c>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.2493333333</v>
+        <v>0.2398666667</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2061,7 +2064,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="13"/>
+      <c r="N34" s="14"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2247,89 +2250,89 @@
       <c r="Q37" s="8">
         <v>0.303</v>
       </c>
-      <c r="R37" s="11">
+      <c r="R37" s="12">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="12">
+      <c r="S37" s="13">
         <v>0.1111</v>
       </c>
-      <c r="T37" s="11"/>
-      <c r="U37" s="11"/>
-      <c r="V37" s="11"/>
-      <c r="W37" s="11"/>
-      <c r="X37" s="11"/>
-      <c r="Y37" s="11"/>
+      <c r="T37" s="12"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="12"/>
       <c r="Z37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="12">
         <v>0.4375</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="12">
         <v>0.4</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="12">
         <v>0.4</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="12">
         <v>0.4</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="12">
         <v>0.4167</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="12">
         <v>0.4</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="12">
         <v>0.4211</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="12">
         <v>0.451</v>
       </c>
-      <c r="J38" s="11">
+      <c r="J38" s="12">
         <v>0.5161</v>
       </c>
-      <c r="K38" s="11">
+      <c r="K38" s="12">
         <v>0.5128</v>
       </c>
-      <c r="L38" s="11">
+      <c r="L38" s="12">
         <v>0.3913</v>
       </c>
-      <c r="M38" s="11">
+      <c r="M38" s="12">
         <v>0.46</v>
       </c>
-      <c r="N38" s="11">
+      <c r="N38" s="12">
         <v>0.325</v>
       </c>
-      <c r="O38" s="11">
+      <c r="O38" s="12">
         <v>0.3333</v>
       </c>
-      <c r="P38" s="11">
+      <c r="P38" s="12">
         <v>0.2564</v>
       </c>
-      <c r="Q38" s="11">
+      <c r="Q38" s="12">
         <v>0.3238</v>
       </c>
-      <c r="R38" s="11">
+      <c r="R38" s="12">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="11">
+      <c r="S38" s="12">
         <v>0.1974</v>
       </c>
-      <c r="T38" s="12">
-        <v>0.1053</v>
-      </c>
-      <c r="U38" s="11"/>
-      <c r="V38" s="11"/>
-      <c r="W38" s="11"/>
-      <c r="X38" s="11"/>
-      <c r="Y38" s="11"/>
-      <c r="Z38" s="11">
+      <c r="T38" s="13">
+        <v>0.0741</v>
+      </c>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.1819666667</v>
+        <v>0.1715666667</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2458,7 +2461,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="13"/>
+      <c r="L44" s="14"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2484,7 +2487,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="17"/>
+      <c r="I45" s="18"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2502,61 +2505,61 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="11"/>
-      <c r="T45" s="11"/>
-      <c r="U45" s="11"/>
-      <c r="V45" s="11"/>
-      <c r="W45" s="11"/>
-      <c r="X45" s="11"/>
-      <c r="Y45" s="11"/>
-      <c r="Z45" s="11"/>
+      <c r="S45" s="12"/>
+      <c r="T45" s="12"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12"/>
+      <c r="Y45" s="12"/>
+      <c r="Z45" s="12"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12">
         <v>0.1111</v>
       </c>
-      <c r="Q46" s="11">
+      <c r="Q46" s="12">
         <v>0.2828</v>
       </c>
-      <c r="R46" s="11">
+      <c r="R46" s="12">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="11">
+      <c r="S46" s="12">
         <v>0.1705</v>
       </c>
-      <c r="T46" s="12">
-        <v>0.127</v>
-      </c>
-      <c r="U46" s="11"/>
-      <c r="V46" s="11"/>
-      <c r="W46" s="11"/>
-      <c r="X46" s="11"/>
-      <c r="Y46" s="11"/>
-      <c r="Z46" s="11">
+      <c r="T46" s="13">
+        <v>0.1429</v>
+      </c>
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="12"/>
+      <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.1880666667</v>
+        <v>0.1933666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="Q47" s="11"/>
-      <c r="R47" s="11"/>
+      <c r="Q47" s="12"/>
+      <c r="R47" s="12"/>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
@@ -2724,56 +2727,56 @@
       <c r="R53" s="8">
         <v>0.2857</v>
       </c>
-      <c r="S53" s="12">
+      <c r="S53" s="13">
         <v>0.093</v>
       </c>
-      <c r="T53" s="11"/>
-      <c r="U53" s="11"/>
-      <c r="V53" s="11"/>
-      <c r="W53" s="11"/>
-      <c r="X53" s="11"/>
-      <c r="Y53" s="11"/>
-      <c r="Z53" s="11"/>
+      <c r="T53" s="12"/>
+      <c r="U53" s="12"/>
+      <c r="V53" s="12"/>
+      <c r="W53" s="12"/>
+      <c r="X53" s="12"/>
+      <c r="Y53" s="12"/>
+      <c r="Z53" s="12"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11"/>
-      <c r="P54" s="11"/>
-      <c r="Q54" s="11">
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
+      <c r="P54" s="12"/>
+      <c r="Q54" s="12">
         <v>0.2727</v>
       </c>
-      <c r="R54" s="11">
+      <c r="R54" s="12">
         <v>0.296</v>
       </c>
-      <c r="S54" s="11">
+      <c r="S54" s="12">
         <v>0.192</v>
       </c>
-      <c r="T54" s="12">
-        <v>0.1935</v>
-      </c>
-      <c r="U54" s="11"/>
-      <c r="V54" s="11"/>
-      <c r="W54" s="11"/>
-      <c r="X54" s="11"/>
-      <c r="Y54" s="11"/>
-      <c r="Z54" s="11">
+      <c r="T54" s="13">
+        <v>0.1636</v>
+      </c>
+      <c r="U54" s="12"/>
+      <c r="V54" s="12"/>
+      <c r="W54" s="12"/>
+      <c r="X54" s="12"/>
+      <c r="Y54" s="12"/>
+      <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.2271666667</v>
+        <v>0.2172</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -2813,7 +2816,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="13"/>
+      <c r="L58" s="14"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -2855,57 +2858,57 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="11"/>
-      <c r="P61" s="11"/>
-      <c r="Q61" s="11"/>
-      <c r="R61" s="11"/>
-      <c r="S61" s="11"/>
-      <c r="T61" s="11"/>
-      <c r="U61" s="11"/>
-      <c r="V61" s="11"/>
-      <c r="W61" s="11"/>
-      <c r="X61" s="11"/>
-      <c r="Y61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
+      <c r="P61" s="12"/>
+      <c r="Q61" s="12"/>
+      <c r="R61" s="12"/>
+      <c r="S61" s="12"/>
+      <c r="T61" s="12"/>
+      <c r="U61" s="12"/>
+      <c r="V61" s="12"/>
+      <c r="W61" s="12"/>
+      <c r="X61" s="12"/>
+      <c r="Y61" s="12"/>
       <c r="Z61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="11"/>
-      <c r="P62" s="11"/>
-      <c r="Q62" s="11"/>
-      <c r="R62" s="11"/>
-      <c r="S62" s="11"/>
-      <c r="T62" s="11"/>
-      <c r="U62" s="11"/>
-      <c r="V62" s="11"/>
-      <c r="W62" s="11"/>
-      <c r="X62" s="11"/>
-      <c r="Y62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="P62" s="12"/>
+      <c r="Q62" s="12"/>
+      <c r="R62" s="12"/>
+      <c r="S62" s="12"/>
+      <c r="T62" s="12"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12"/>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="12"/>
       <c r="Z62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -3084,8 +3087,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="18"/>
-      <c r="T65" s="18"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3184,71 +3187,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="20">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="19">
+      <c r="C67" s="20">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="20">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="19">
+      <c r="F67" s="20">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="19">
+      <c r="G67" s="20">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="19">
+      <c r="H67" s="20">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="19">
+      <c r="I67" s="20">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="19">
+      <c r="J67" s="20">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="19">
+      <c r="K67" s="20">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="20">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="19">
+      <c r="M67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="19">
+      <c r="N67" s="20">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="19">
+      <c r="O67" s="20">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="19">
+      <c r="P67" s="20">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="19">
+      <c r="Q67" s="20">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="19">
+      <c r="R67" s="20">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3259,7 +3262,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="19">
+      <c r="Z67" s="20">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3352,85 +3355,85 @@
       <c r="A69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="12">
         <f t="shared" ref="B69:S69" si="13">average(B53,B45,B37,B29,B21,B13,B5)</f>
         <v>0.3444333333</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="12">
         <f t="shared" si="13"/>
         <v>0.309525</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="12">
         <f t="shared" si="13"/>
         <v>0.42125</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E69" s="12">
         <f t="shared" si="13"/>
         <v>0.42478</v>
       </c>
-      <c r="F69" s="11">
+      <c r="F69" s="12">
         <f t="shared" si="13"/>
         <v>0.40488</v>
       </c>
-      <c r="G69" s="11">
+      <c r="G69" s="12">
         <f t="shared" si="13"/>
         <v>0.45414</v>
       </c>
-      <c r="H69" s="11">
+      <c r="H69" s="12">
         <f t="shared" si="13"/>
         <v>0.40556</v>
       </c>
-      <c r="I69" s="11">
+      <c r="I69" s="12">
         <f t="shared" si="13"/>
         <v>0.31688</v>
       </c>
-      <c r="J69" s="11">
+      <c r="J69" s="12">
         <f t="shared" si="13"/>
         <v>0.41248</v>
       </c>
-      <c r="K69" s="11">
+      <c r="K69" s="12">
         <f t="shared" si="13"/>
         <v>0.29162</v>
       </c>
-      <c r="L69" s="11">
+      <c r="L69" s="12">
         <f t="shared" si="13"/>
         <v>0.35694</v>
       </c>
-      <c r="M69" s="11">
+      <c r="M69" s="12">
         <f t="shared" si="13"/>
         <v>0.3687333333</v>
       </c>
-      <c r="N69" s="11">
+      <c r="N69" s="12">
         <f t="shared" si="13"/>
         <v>0.26642</v>
       </c>
-      <c r="O69" s="11">
+      <c r="O69" s="12">
         <f t="shared" si="13"/>
         <v>0.2291666667</v>
       </c>
-      <c r="P69" s="11">
+      <c r="P69" s="12">
         <f t="shared" si="13"/>
         <v>0.3634</v>
       </c>
-      <c r="Q69" s="11">
+      <c r="Q69" s="12">
         <f t="shared" si="13"/>
         <v>0.2847571429</v>
       </c>
-      <c r="R69" s="11">
+      <c r="R69" s="12">
         <f t="shared" si="13"/>
         <v>0.15246</v>
       </c>
-      <c r="S69" s="11">
+      <c r="S69" s="12">
         <f t="shared" si="13"/>
         <v>0.08064</v>
       </c>
-      <c r="T69" s="11"/>
+      <c r="T69" s="12"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
-      <c r="Z69" s="11">
+      <c r="Z69" s="12">
         <f>average(R69:Y69)</f>
         <v>0.11655</v>
       </c>
@@ -3439,81 +3442,81 @@
       <c r="A70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="11">
+      <c r="B70" s="12">
         <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="12">
         <f t="shared" si="14"/>
         <v>0.366525</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="12">
         <f t="shared" si="14"/>
         <v>0.30455</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="12">
         <f t="shared" si="14"/>
         <v>0.38494</v>
       </c>
-      <c r="F70" s="11">
+      <c r="F70" s="12">
         <f t="shared" si="14"/>
         <v>0.40984</v>
       </c>
-      <c r="G70" s="11">
+      <c r="G70" s="12">
         <f t="shared" si="14"/>
         <v>0.4393</v>
       </c>
-      <c r="H70" s="11">
+      <c r="H70" s="12">
         <f t="shared" si="14"/>
         <v>0.42082</v>
       </c>
-      <c r="I70" s="11">
+      <c r="I70" s="12">
         <f t="shared" si="14"/>
         <v>0.4131</v>
       </c>
-      <c r="J70" s="11">
+      <c r="J70" s="12">
         <f t="shared" si="14"/>
         <v>0.3999</v>
       </c>
-      <c r="K70" s="11">
+      <c r="K70" s="12">
         <f t="shared" si="14"/>
         <v>0.38592</v>
       </c>
-      <c r="L70" s="11">
+      <c r="L70" s="12">
         <f t="shared" si="14"/>
         <v>0.33754</v>
       </c>
-      <c r="M70" s="11">
+      <c r="M70" s="12">
         <f t="shared" si="14"/>
         <v>0.34014</v>
       </c>
-      <c r="N70" s="11">
+      <c r="N70" s="12">
         <f t="shared" si="14"/>
         <v>0.30044</v>
       </c>
-      <c r="O70" s="11">
+      <c r="O70" s="12">
         <f t="shared" si="14"/>
         <v>0.30184</v>
       </c>
-      <c r="P70" s="11">
+      <c r="P70" s="12">
         <f t="shared" si="14"/>
         <v>0.2368833333</v>
       </c>
-      <c r="Q70" s="11">
+      <c r="Q70" s="12">
         <f t="shared" si="14"/>
         <v>0.3044714286</v>
       </c>
-      <c r="R70" s="11">
+      <c r="R70" s="12">
         <f t="shared" si="14"/>
         <v>0.2830428571</v>
       </c>
-      <c r="S70" s="11">
+      <c r="S70" s="12">
         <f t="shared" si="14"/>
         <v>0.2062</v>
       </c>
-      <c r="T70" s="11">
+      <c r="T70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1515285714</v>
+        <v>0.1261285714</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3526,30 +3529,30 @@
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="1"/>
-      <c r="S79" s="11"/>
+      <c r="S79" s="12"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="1"/>
-      <c r="S80" s="11"/>
+      <c r="S80" s="12"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="1"/>
-      <c r="S81" s="11"/>
+      <c r="S81" s="12"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="1"/>
-      <c r="S82" s="11"/>
+      <c r="S82" s="12"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="1"/>
-      <c r="S83" s="11"/>
+      <c r="S83" s="12"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="1"/>
-      <c r="S84" s="11"/>
+      <c r="S84" s="12"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="S85" s="11"/>
+      <c r="S85" s="12"/>
     </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
@@ -3578,67 +3581,67 @@
       <c r="B109" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="11" t="str">
+      <c r="C109" s="12" t="str">
         <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D109" s="11" t="str">
+      <c r="D109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E109" s="11" t="str">
+      <c r="E109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F109" s="11" t="str">
+      <c r="F109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G109" s="11" t="str">
+      <c r="G109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H109" s="11" t="str">
+      <c r="H109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I109" s="11" t="str">
+      <c r="I109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J109" s="11" t="str">
+      <c r="J109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K109" s="11" t="str">
+      <c r="K109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L109" s="11" t="str">
+      <c r="L109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M109" s="11" t="str">
+      <c r="M109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N109" s="11" t="str">
+      <c r="N109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O109" s="11" t="str">
+      <c r="O109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P109" s="11" t="str">
+      <c r="P109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q109" s="11" t="str">
+      <c r="Q109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R109" s="11" t="str">
+      <c r="R109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -700,7 +700,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.0968</v>
+        <v>0.1515</v>
       </c>
       <c r="T5" s="11"/>
       <c r="U5" s="9"/>
@@ -710,7 +710,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.2452166667</v>
+        <v>0.2543333333</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -772,7 +772,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="13">
-        <v>0.1867</v>
+        <v>0.1831</v>
       </c>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
@@ -781,7 +781,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2586714286</v>
+        <v>0.2581571429</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1098,7 +1098,7 @@
         <v>0.0513</v>
       </c>
       <c r="S13" s="13">
-        <v>0.0435</v>
+        <v>0.16</v>
       </c>
       <c r="T13" s="15"/>
       <c r="W13" s="16"/>
@@ -1163,7 +1163,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="13">
-        <v>0.099</v>
+        <v>0.1188</v>
       </c>
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
@@ -1172,7 +1172,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.2013333333</v>
+        <v>0.2079333333</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1478,7 +1478,9 @@
         <v>0.22</v>
       </c>
       <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
+      <c r="S21" s="13">
+        <v>0.1</v>
+      </c>
       <c r="T21" s="12"/>
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
@@ -1540,7 +1542,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="13">
-        <v>0.0575</v>
+        <v>0.0617</v>
       </c>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
@@ -1549,7 +1551,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1446</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1863,7 +1865,7 @@
       </c>
       <c r="R29" s="12"/>
       <c r="S29" s="13">
-        <v>0.0588</v>
+        <v>0.1111</v>
       </c>
       <c r="T29" s="17"/>
       <c r="U29" s="12"/>
@@ -1930,7 +1932,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="13">
-        <v>0.1591</v>
+        <v>0.1304</v>
       </c>
       <c r="U30" s="12"/>
       <c r="V30" s="12"/>
@@ -1939,7 +1941,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.2398666667</v>
+        <v>0.2303</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2253,9 +2255,7 @@
       <c r="R37" s="12">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="13">
-        <v>0.1111</v>
-      </c>
+      <c r="S37" s="13"/>
       <c r="T37" s="12"/>
       <c r="U37" s="12"/>
       <c r="V37" s="12"/>
@@ -2323,7 +2323,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="13">
-        <v>0.0741</v>
+        <v>0.087</v>
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="12"/>
@@ -2332,7 +2332,7 @@
       <c r="Y38" s="12"/>
       <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.1715666667</v>
+        <v>0.1758666667</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2505,7 +2505,9 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="12"/>
+      <c r="S45" s="13">
+        <v>0.0714</v>
+      </c>
       <c r="T45" s="12"/>
       <c r="U45" s="12"/>
       <c r="V45" s="12"/>
@@ -2728,7 +2730,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="13">
-        <v>0.093</v>
+        <v>0.122</v>
       </c>
       <c r="T53" s="12"/>
       <c r="U53" s="12"/>
@@ -2767,7 +2769,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="13">
-        <v>0.1636</v>
+        <v>0.1504</v>
       </c>
       <c r="U54" s="12"/>
       <c r="V54" s="12"/>
@@ -2776,7 +2778,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.2172</v>
+        <v>0.2128</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3425,7 +3427,7 @@
       </c>
       <c r="S69" s="12">
         <f t="shared" si="13"/>
-        <v>0.08064</v>
+        <v>0.1193333333</v>
       </c>
       <c r="T69" s="12"/>
       <c r="U69" s="3"/>
@@ -3435,7 +3437,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="12">
         <f>average(R69:Y69)</f>
-        <v>0.11655</v>
+        <v>0.1358966667</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3516,7 +3518,7 @@
       </c>
       <c r="T70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1261285714</v>
+        <v>0.1249</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -155,12 +155,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -699,10 +693,10 @@
       <c r="R5" s="8">
         <v>0.1923</v>
       </c>
-      <c r="S5" s="10">
+      <c r="S5" s="8">
         <v>0.1515</v>
       </c>
-      <c r="T5" s="11"/>
+      <c r="T5" s="9"/>
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -717,71 +711,73 @@
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>0.5714</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <v>0.4167</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="10">
         <v>0.3182</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>0.3333</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>0.3429</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="10">
         <v>0.4348</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="10">
         <v>0.4468</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="10">
         <v>0.3462</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="10">
         <v>0.2456</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="10">
         <v>0.2203</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="10">
         <v>0.2537</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="10">
         <v>0.2593</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="10">
         <v>0.2368</v>
       </c>
-      <c r="O6" s="12">
+      <c r="O6" s="10">
         <v>0.2308</v>
       </c>
-      <c r="P6" s="12">
+      <c r="P6" s="10">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="10">
         <v>0.3393</v>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="10">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="10">
         <v>0.2745</v>
       </c>
-      <c r="T6" s="13">
+      <c r="T6" s="10">
         <v>0.1831</v>
       </c>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12">
+      <c r="U6" s="11">
+        <v>0.1774</v>
+      </c>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10">
         <f t="shared" si="2"/>
-        <v>0.2581571429</v>
+        <v>0.2480625</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -919,7 +915,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="14"/>
+      <c r="W10" s="12"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -978,7 +974,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="14"/>
+      <c r="W11" s="12"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1036,7 +1032,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="14"/>
+      <c r="W12" s="12"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1097,103 +1093,105 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="13">
+      <c r="S13" s="10">
         <v>0.16</v>
       </c>
-      <c r="T13" s="15"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="12"/>
+      <c r="T13" s="13"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10">
         <v>0.5161</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="10">
         <v>0.3333</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="10">
         <v>0.34</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="10">
         <v>0.3521</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="10">
         <v>0.4125</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="10">
         <v>0.4321</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="10">
         <v>0.369</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="10">
         <v>0.3194</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="10">
         <v>0.2969</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="10">
         <v>0.32</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="10">
         <v>0.3205</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="10">
         <v>0.3571</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O14" s="10">
         <v>0.449</v>
       </c>
-      <c r="P14" s="12">
+      <c r="P14" s="10">
         <v>0.4182</v>
       </c>
-      <c r="Q14" s="12">
+      <c r="Q14" s="10">
         <v>0.3269</v>
       </c>
-      <c r="R14" s="12">
+      <c r="R14" s="10">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="12">
+      <c r="S14" s="10">
         <v>0.2339</v>
       </c>
-      <c r="T14" s="13">
+      <c r="T14" s="10">
         <v>0.1188</v>
       </c>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12">
+      <c r="U14" s="11">
+        <v>0.1023</v>
+      </c>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10">
         <f>average(R14:Y14)</f>
-        <v>0.2079333333</v>
+        <v>0.181525</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="S15" s="12"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="12"/>
-      <c r="Z15" s="12"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="12"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
@@ -1477,81 +1475,83 @@
       <c r="Q21" s="8">
         <v>0.22</v>
       </c>
-      <c r="R21" s="12"/>
-      <c r="S21" s="13">
+      <c r="R21" s="10"/>
+      <c r="S21" s="10">
         <v>0.1</v>
       </c>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
       <c r="Z21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10">
         <v>0.5</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="10">
         <v>0.5625</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="10">
         <v>0.5714</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="10">
         <v>0.4815</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="10">
         <v>0.4634</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="10">
         <v>0.4898</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="10">
         <v>0.463</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="10">
         <v>0.377</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="10">
         <v>0.3387</v>
       </c>
-      <c r="N22" s="12">
+      <c r="N22" s="10">
         <v>0.3265</v>
       </c>
-      <c r="O22" s="12">
+      <c r="O22" s="10">
         <v>0.3056</v>
       </c>
-      <c r="P22" s="12">
+      <c r="P22" s="10">
         <v>0.2075</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="10">
         <v>0.2615</v>
       </c>
-      <c r="R22" s="12">
+      <c r="R22" s="10">
         <v>0.232</v>
       </c>
-      <c r="S22" s="12">
+      <c r="S22" s="10">
         <v>0.1443</v>
       </c>
-      <c r="T22" s="13">
+      <c r="T22" s="10">
         <v>0.0617</v>
       </c>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12">
+      <c r="U22" s="11">
+        <v>0.08</v>
+      </c>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="10">
         <f>average(R22:Y22)</f>
-        <v>0.146</v>
+        <v>0.1295</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1748,7 +1748,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="14"/>
+      <c r="W27" s="12"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1806,8 +1806,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="15"/>
-      <c r="W28" s="14"/>
+      <c r="T28" s="13"/>
+      <c r="W28" s="12"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1863,85 +1863,87 @@
       <c r="Q29" s="8">
         <v>0.2759</v>
       </c>
-      <c r="R29" s="12"/>
-      <c r="S29" s="13">
+      <c r="R29" s="10"/>
+      <c r="S29" s="10">
         <v>0.1111</v>
       </c>
-      <c r="T29" s="17"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
       <c r="Z29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10">
         <v>0.1333</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="10">
         <v>0.1667</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="10">
         <v>0.3514</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="10">
         <v>0.375</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="10">
         <v>0.3778</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="10">
         <v>0.3226</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="10">
         <v>0.4359</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="10">
         <v>0.4286</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="10">
         <v>0.4366</v>
       </c>
-      <c r="L30" s="12">
+      <c r="L30" s="10">
         <v>0.3457</v>
       </c>
-      <c r="M30" s="12">
+      <c r="M30" s="10">
         <v>0.3222</v>
       </c>
-      <c r="N30" s="12">
+      <c r="N30" s="10">
         <v>0.2568</v>
       </c>
-      <c r="O30" s="12">
+      <c r="O30" s="10">
         <v>0.1905</v>
       </c>
-      <c r="P30" s="12">
+      <c r="P30" s="10">
         <v>0.2281</v>
       </c>
-      <c r="Q30" s="12">
+      <c r="Q30" s="10">
         <v>0.3243</v>
       </c>
-      <c r="R30" s="12">
+      <c r="R30" s="10">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="12">
+      <c r="S30" s="10">
         <v>0.2308</v>
       </c>
-      <c r="T30" s="13">
+      <c r="T30" s="10">
         <v>0.1304</v>
       </c>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="12">
+      <c r="U30" s="11">
+        <v>0.102</v>
+      </c>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10">
         <f>average(R30:Y30)</f>
-        <v>0.2303</v>
+        <v>0.198225</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2066,7 +2068,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="14"/>
+      <c r="N34" s="12"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2252,87 +2254,89 @@
       <c r="Q37" s="8">
         <v>0.303</v>
       </c>
-      <c r="R37" s="12">
+      <c r="R37" s="10">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="13"/>
-      <c r="T37" s="12"/>
-      <c r="U37" s="12"/>
-      <c r="V37" s="12"/>
-      <c r="W37" s="12"/>
-      <c r="X37" s="12"/>
-      <c r="Y37" s="12"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="10"/>
+      <c r="X37" s="10"/>
+      <c r="Y37" s="10"/>
       <c r="Z37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="10">
         <v>0.4375</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="10">
         <v>0.4</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="10">
         <v>0.4</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="10">
         <v>0.4</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="10">
         <v>0.4167</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="10">
         <v>0.4</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="10">
         <v>0.4211</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="10">
         <v>0.451</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J38" s="10">
         <v>0.5161</v>
       </c>
-      <c r="K38" s="12">
+      <c r="K38" s="10">
         <v>0.5128</v>
       </c>
-      <c r="L38" s="12">
+      <c r="L38" s="10">
         <v>0.3913</v>
       </c>
-      <c r="M38" s="12">
+      <c r="M38" s="10">
         <v>0.46</v>
       </c>
-      <c r="N38" s="12">
+      <c r="N38" s="10">
         <v>0.325</v>
       </c>
-      <c r="O38" s="12">
+      <c r="O38" s="10">
         <v>0.3333</v>
       </c>
-      <c r="P38" s="12">
+      <c r="P38" s="10">
         <v>0.2564</v>
       </c>
-      <c r="Q38" s="12">
+      <c r="Q38" s="10">
         <v>0.3238</v>
       </c>
-      <c r="R38" s="12">
+      <c r="R38" s="10">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="12">
+      <c r="S38" s="10">
         <v>0.1974</v>
       </c>
-      <c r="T38" s="13">
+      <c r="T38" s="10">
         <v>0.087</v>
       </c>
-      <c r="U38" s="12"/>
-      <c r="V38" s="12"/>
-      <c r="W38" s="12"/>
-      <c r="X38" s="12"/>
-      <c r="Y38" s="12"/>
-      <c r="Z38" s="12">
+      <c r="U38" s="11">
+        <v>0.0833</v>
+      </c>
+      <c r="V38" s="10"/>
+      <c r="W38" s="10"/>
+      <c r="X38" s="10"/>
+      <c r="Y38" s="10"/>
+      <c r="Z38" s="10">
         <f>average(R38:Y38)</f>
-        <v>0.1758666667</v>
+        <v>0.152725</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2461,7 +2465,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="14"/>
+      <c r="L44" s="12"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2487,7 +2491,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="18"/>
+      <c r="I45" s="16"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2505,63 +2509,65 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="13">
+      <c r="S45" s="10">
         <v>0.0714</v>
       </c>
-      <c r="T45" s="12"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="12"/>
-      <c r="W45" s="12"/>
-      <c r="X45" s="12"/>
-      <c r="Y45" s="12"/>
-      <c r="Z45" s="12"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
+      <c r="V45" s="10"/>
+      <c r="W45" s="10"/>
+      <c r="X45" s="10"/>
+      <c r="Y45" s="10"/>
+      <c r="Z45" s="10"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10">
         <v>0.1111</v>
       </c>
-      <c r="Q46" s="12">
+      <c r="Q46" s="10">
         <v>0.2828</v>
       </c>
-      <c r="R46" s="12">
+      <c r="R46" s="10">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="12">
+      <c r="S46" s="10">
         <v>0.1705</v>
       </c>
-      <c r="T46" s="13">
+      <c r="T46" s="10">
         <v>0.1429</v>
       </c>
-      <c r="U46" s="12"/>
-      <c r="V46" s="12"/>
-      <c r="W46" s="12"/>
-      <c r="X46" s="12"/>
-      <c r="Y46" s="12"/>
-      <c r="Z46" s="12">
+      <c r="U46" s="11">
+        <v>0.1136</v>
+      </c>
+      <c r="V46" s="10"/>
+      <c r="W46" s="10"/>
+      <c r="X46" s="10"/>
+      <c r="Y46" s="10"/>
+      <c r="Z46" s="10">
         <f>average(R46:Y46)</f>
-        <v>0.1933666667</v>
+        <v>0.173425</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="Q47" s="12"/>
-      <c r="R47" s="12"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
@@ -2729,56 +2735,58 @@
       <c r="R53" s="8">
         <v>0.2857</v>
       </c>
-      <c r="S53" s="13">
+      <c r="S53" s="10">
         <v>0.122</v>
       </c>
-      <c r="T53" s="12"/>
-      <c r="U53" s="12"/>
-      <c r="V53" s="12"/>
-      <c r="W53" s="12"/>
-      <c r="X53" s="12"/>
-      <c r="Y53" s="12"/>
-      <c r="Z53" s="12"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
+      <c r="X53" s="10"/>
+      <c r="Y53" s="10"/>
+      <c r="Z53" s="10"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-      <c r="N54" s="12"/>
-      <c r="O54" s="12"/>
-      <c r="P54" s="12"/>
-      <c r="Q54" s="12">
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10">
         <v>0.2727</v>
       </c>
-      <c r="R54" s="12">
+      <c r="R54" s="10">
         <v>0.296</v>
       </c>
-      <c r="S54" s="12">
+      <c r="S54" s="10">
         <v>0.192</v>
       </c>
-      <c r="T54" s="13">
+      <c r="T54" s="10">
         <v>0.1504</v>
       </c>
-      <c r="U54" s="12"/>
-      <c r="V54" s="12"/>
-      <c r="W54" s="12"/>
-      <c r="X54" s="12"/>
-      <c r="Y54" s="12"/>
-      <c r="Z54" s="12">
+      <c r="U54" s="11">
+        <v>0.1359</v>
+      </c>
+      <c r="V54" s="10"/>
+      <c r="W54" s="10"/>
+      <c r="X54" s="10"/>
+      <c r="Y54" s="10"/>
+      <c r="Z54" s="10">
         <f>average(R54:Y54)</f>
-        <v>0.2128</v>
+        <v>0.193575</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -2818,7 +2826,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="14"/>
+      <c r="L58" s="12"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -2860,57 +2868,57 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12"/>
-      <c r="L61" s="12"/>
-      <c r="M61" s="12"/>
-      <c r="N61" s="12"/>
-      <c r="O61" s="12"/>
-      <c r="P61" s="12"/>
-      <c r="Q61" s="12"/>
-      <c r="R61" s="12"/>
-      <c r="S61" s="12"/>
-      <c r="T61" s="12"/>
-      <c r="U61" s="12"/>
-      <c r="V61" s="12"/>
-      <c r="W61" s="12"/>
-      <c r="X61" s="12"/>
-      <c r="Y61" s="12"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
+      <c r="V61" s="10"/>
+      <c r="W61" s="10"/>
+      <c r="X61" s="10"/>
+      <c r="Y61" s="10"/>
       <c r="Z61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="12"/>
-      <c r="L62" s="12"/>
-      <c r="M62" s="12"/>
-      <c r="N62" s="12"/>
-      <c r="O62" s="12"/>
-      <c r="P62" s="12"/>
-      <c r="Q62" s="12"/>
-      <c r="R62" s="12"/>
-      <c r="S62" s="12"/>
-      <c r="T62" s="12"/>
-      <c r="U62" s="12"/>
-      <c r="V62" s="12"/>
-      <c r="W62" s="12"/>
-      <c r="X62" s="12"/>
-      <c r="Y62" s="12"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="10"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="10"/>
+      <c r="X62" s="10"/>
+      <c r="Y62" s="10"/>
       <c r="Z62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -3089,8 +3097,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="19"/>
-      <c r="T65" s="19"/>
+      <c r="S65" s="17"/>
+      <c r="T65" s="17"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3189,71 +3197,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="18">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="20">
+      <c r="C67" s="18">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="18">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="18">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="20">
+      <c r="G67" s="18">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="20">
+      <c r="H67" s="18">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="20">
+      <c r="I67" s="18">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="20">
+      <c r="J67" s="18">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="20">
+      <c r="K67" s="18">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="20">
+      <c r="L67" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="20">
+      <c r="M67" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="20">
+      <c r="N67" s="18">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="20">
+      <c r="O67" s="18">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="20">
+      <c r="P67" s="18">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="20">
+      <c r="Q67" s="18">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="20">
+      <c r="R67" s="18">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3264,7 +3272,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="20">
+      <c r="Z67" s="18">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3357,85 +3365,85 @@
       <c r="A69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="10">
         <f t="shared" ref="B69:S69" si="13">average(B53,B45,B37,B29,B21,B13,B5)</f>
         <v>0.3444333333</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="10">
         <f t="shared" si="13"/>
         <v>0.309525</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="10">
         <f t="shared" si="13"/>
         <v>0.42125</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="10">
         <f t="shared" si="13"/>
         <v>0.42478</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="10">
         <f t="shared" si="13"/>
         <v>0.40488</v>
       </c>
-      <c r="G69" s="12">
+      <c r="G69" s="10">
         <f t="shared" si="13"/>
         <v>0.45414</v>
       </c>
-      <c r="H69" s="12">
+      <c r="H69" s="10">
         <f t="shared" si="13"/>
         <v>0.40556</v>
       </c>
-      <c r="I69" s="12">
+      <c r="I69" s="10">
         <f t="shared" si="13"/>
         <v>0.31688</v>
       </c>
-      <c r="J69" s="12">
+      <c r="J69" s="10">
         <f t="shared" si="13"/>
         <v>0.41248</v>
       </c>
-      <c r="K69" s="12">
+      <c r="K69" s="10">
         <f t="shared" si="13"/>
         <v>0.29162</v>
       </c>
-      <c r="L69" s="12">
+      <c r="L69" s="10">
         <f t="shared" si="13"/>
         <v>0.35694</v>
       </c>
-      <c r="M69" s="12">
+      <c r="M69" s="10">
         <f t="shared" si="13"/>
         <v>0.3687333333</v>
       </c>
-      <c r="N69" s="12">
+      <c r="N69" s="10">
         <f t="shared" si="13"/>
         <v>0.26642</v>
       </c>
-      <c r="O69" s="12">
+      <c r="O69" s="10">
         <f t="shared" si="13"/>
         <v>0.2291666667</v>
       </c>
-      <c r="P69" s="12">
+      <c r="P69" s="10">
         <f t="shared" si="13"/>
         <v>0.3634</v>
       </c>
-      <c r="Q69" s="12">
+      <c r="Q69" s="10">
         <f t="shared" si="13"/>
         <v>0.2847571429</v>
       </c>
-      <c r="R69" s="12">
+      <c r="R69" s="10">
         <f t="shared" si="13"/>
         <v>0.15246</v>
       </c>
-      <c r="S69" s="12">
+      <c r="S69" s="10">
         <f t="shared" si="13"/>
         <v>0.1193333333</v>
       </c>
-      <c r="T69" s="12"/>
+      <c r="T69" s="10"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
-      <c r="Z69" s="12">
+      <c r="Z69" s="10">
         <f>average(R69:Y69)</f>
         <v>0.1358966667</v>
       </c>
@@ -3444,79 +3452,79 @@
       <c r="A70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="12">
+      <c r="B70" s="10">
         <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="10">
         <f t="shared" si="14"/>
         <v>0.366525</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="10">
         <f t="shared" si="14"/>
         <v>0.30455</v>
       </c>
-      <c r="E70" s="12">
+      <c r="E70" s="10">
         <f t="shared" si="14"/>
         <v>0.38494</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="10">
         <f t="shared" si="14"/>
         <v>0.40984</v>
       </c>
-      <c r="G70" s="12">
+      <c r="G70" s="10">
         <f t="shared" si="14"/>
         <v>0.4393</v>
       </c>
-      <c r="H70" s="12">
+      <c r="H70" s="10">
         <f t="shared" si="14"/>
         <v>0.42082</v>
       </c>
-      <c r="I70" s="12">
+      <c r="I70" s="10">
         <f t="shared" si="14"/>
         <v>0.4131</v>
       </c>
-      <c r="J70" s="12">
+      <c r="J70" s="10">
         <f t="shared" si="14"/>
         <v>0.3999</v>
       </c>
-      <c r="K70" s="12">
+      <c r="K70" s="10">
         <f t="shared" si="14"/>
         <v>0.38592</v>
       </c>
-      <c r="L70" s="12">
+      <c r="L70" s="10">
         <f t="shared" si="14"/>
         <v>0.33754</v>
       </c>
-      <c r="M70" s="12">
+      <c r="M70" s="10">
         <f t="shared" si="14"/>
         <v>0.34014</v>
       </c>
-      <c r="N70" s="12">
+      <c r="N70" s="10">
         <f t="shared" si="14"/>
         <v>0.30044</v>
       </c>
-      <c r="O70" s="12">
+      <c r="O70" s="10">
         <f t="shared" si="14"/>
         <v>0.30184</v>
       </c>
-      <c r="P70" s="12">
+      <c r="P70" s="10">
         <f t="shared" si="14"/>
         <v>0.2368833333</v>
       </c>
-      <c r="Q70" s="12">
+      <c r="Q70" s="10">
         <f t="shared" si="14"/>
         <v>0.3044714286</v>
       </c>
-      <c r="R70" s="12">
+      <c r="R70" s="10">
         <f t="shared" si="14"/>
         <v>0.2830428571</v>
       </c>
-      <c r="S70" s="12">
+      <c r="S70" s="10">
         <f t="shared" si="14"/>
         <v>0.2062</v>
       </c>
-      <c r="T70" s="12">
+      <c r="T70" s="10">
         <f t="shared" si="14"/>
         <v>0.1249</v>
       </c>
@@ -3531,30 +3539,30 @@
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="1"/>
-      <c r="S79" s="12"/>
+      <c r="S79" s="10"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="1"/>
-      <c r="S80" s="12"/>
+      <c r="S80" s="10"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="1"/>
-      <c r="S81" s="12"/>
+      <c r="S81" s="10"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="1"/>
-      <c r="S82" s="12"/>
+      <c r="S82" s="10"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="1"/>
-      <c r="S83" s="12"/>
+      <c r="S83" s="10"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="1"/>
-      <c r="S84" s="12"/>
+      <c r="S84" s="10"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="S85" s="12"/>
+      <c r="S85" s="10"/>
     </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
@@ -3583,67 +3591,67 @@
       <c r="B109" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="12" t="str">
+      <c r="C109" s="10" t="str">
         <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D109" s="12" t="str">
+      <c r="D109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E109" s="12" t="str">
+      <c r="E109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F109" s="12" t="str">
+      <c r="F109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G109" s="12" t="str">
+      <c r="G109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H109" s="12" t="str">
+      <c r="H109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I109" s="12" t="str">
+      <c r="I109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J109" s="12" t="str">
+      <c r="J109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K109" s="12" t="str">
+      <c r="K109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L109" s="12" t="str">
+      <c r="L109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M109" s="12" t="str">
+      <c r="M109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N109" s="12" t="str">
+      <c r="N109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O109" s="12" t="str">
+      <c r="O109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P109" s="12" t="str">
+      <c r="P109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q109" s="12" t="str">
+      <c r="Q109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R109" s="12" t="str">
+      <c r="R109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -1543,7 +1543,7 @@
         <v>0.0617</v>
       </c>
       <c r="U22" s="11">
-        <v>0.08</v>
+        <v>0.0986</v>
       </c>
       <c r="V22" s="10"/>
       <c r="W22" s="10"/>
@@ -1551,7 +1551,7 @@
       <c r="Y22" s="10"/>
       <c r="Z22" s="10">
         <f>average(R22:Y22)</f>
-        <v>0.1295</v>
+        <v>0.13415</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1935,7 +1935,7 @@
         <v>0.1304</v>
       </c>
       <c r="U30" s="11">
-        <v>0.102</v>
+        <v>0.08</v>
       </c>
       <c r="V30" s="10"/>
       <c r="W30" s="10"/>
@@ -1943,7 +1943,7 @@
       <c r="Y30" s="10"/>
       <c r="Z30" s="10">
         <f>average(R30:Y30)</f>
-        <v>0.198225</v>
+        <v>0.192725</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2328,7 +2328,7 @@
         <v>0.087</v>
       </c>
       <c r="U38" s="11">
-        <v>0.0833</v>
+        <v>0.1</v>
       </c>
       <c r="V38" s="10"/>
       <c r="W38" s="10"/>
@@ -2336,7 +2336,7 @@
       <c r="Y38" s="10"/>
       <c r="Z38" s="10">
         <f>average(R38:Y38)</f>
-        <v>0.152725</v>
+        <v>0.1569</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2554,7 +2554,7 @@
         <v>0.1429</v>
       </c>
       <c r="U46" s="11">
-        <v>0.1136</v>
+        <v>0.05</v>
       </c>
       <c r="V46" s="10"/>
       <c r="W46" s="10"/>
@@ -2562,7 +2562,7 @@
       <c r="Y46" s="10"/>
       <c r="Z46" s="10">
         <f>average(R46:Y46)</f>
-        <v>0.173425</v>
+        <v>0.157525</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2778,7 +2778,7 @@
         <v>0.1504</v>
       </c>
       <c r="U54" s="11">
-        <v>0.1359</v>
+        <v>0.1327</v>
       </c>
       <c r="V54" s="10"/>
       <c r="W54" s="10"/>
@@ -2786,7 +2786,7 @@
       <c r="Y54" s="10"/>
       <c r="Z54" s="10">
         <f>average(R54:Y54)</f>
-        <v>0.193575</v>
+        <v>0.192775</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3453,7 +3453,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="10">
-        <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <f t="shared" ref="B70:U70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
       <c r="C70" s="10">
@@ -3527,6 +3527,10 @@
       <c r="T70" s="10">
         <f t="shared" si="14"/>
         <v>0.1249</v>
+      </c>
+      <c r="U70" s="10">
+        <f t="shared" si="14"/>
+        <v>0.1058571429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -155,6 +155,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -693,10 +699,10 @@
       <c r="R5" s="8">
         <v>0.1923</v>
       </c>
-      <c r="S5" s="8">
+      <c r="S5" s="10">
         <v>0.1515</v>
       </c>
-      <c r="T5" s="9"/>
+      <c r="T5" s="11"/>
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -711,73 +717,71 @@
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="12">
         <v>0.5714</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="12">
         <v>0.4167</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="12">
         <v>0.3182</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="12">
         <v>0.3333</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="12">
         <v>0.3429</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="12">
         <v>0.4348</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="12">
         <v>0.4468</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="12">
         <v>0.3462</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="12">
         <v>0.2456</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="12">
         <v>0.2203</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="12">
         <v>0.2537</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="12">
         <v>0.2593</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="12">
         <v>0.2368</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="12">
         <v>0.2308</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="12">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="12">
         <v>0.3393</v>
       </c>
-      <c r="R6" s="10">
+      <c r="R6" s="12">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="10">
+      <c r="S6" s="12">
         <v>0.2745</v>
       </c>
-      <c r="T6" s="10">
-        <v>0.1831</v>
-      </c>
-      <c r="U6" s="11">
-        <v>0.1774</v>
-      </c>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10">
+      <c r="T6" s="13">
+        <v>0.1538</v>
+      </c>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2480625</v>
+        <v>0.2539714286</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -915,7 +919,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="12"/>
+      <c r="W10" s="14"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -974,7 +978,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="12"/>
+      <c r="W11" s="14"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1032,7 +1036,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="12"/>
+      <c r="W12" s="14"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1093,105 +1097,103 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="10">
+      <c r="S13" s="13">
         <v>0.16</v>
       </c>
-      <c r="T13" s="13"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
+      <c r="T13" s="15"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12">
         <v>0.5161</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="12">
         <v>0.3333</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="12">
         <v>0.34</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="12">
         <v>0.3521</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="12">
         <v>0.4125</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="12">
         <v>0.4321</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="12">
         <v>0.369</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="12">
         <v>0.3194</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="12">
         <v>0.2969</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="12">
         <v>0.32</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="12">
         <v>0.3205</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="12">
         <v>0.3571</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="12">
         <v>0.449</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="12">
         <v>0.4182</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="12">
         <v>0.3269</v>
       </c>
-      <c r="R14" s="10">
+      <c r="R14" s="12">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="10">
+      <c r="S14" s="12">
         <v>0.2339</v>
       </c>
-      <c r="T14" s="10">
-        <v>0.1188</v>
-      </c>
-      <c r="U14" s="11">
-        <v>0.1023</v>
-      </c>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10">
+      <c r="T14" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.181525</v>
+        <v>0.2016666667</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="S15" s="10"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
@@ -1475,83 +1477,81 @@
       <c r="Q21" s="8">
         <v>0.22</v>
       </c>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10">
+      <c r="R21" s="12"/>
+      <c r="S21" s="13">
         <v>0.1</v>
       </c>
-      <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="10"/>
-      <c r="Y21" s="10"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
       <c r="Z21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12">
         <v>0.5</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="12">
         <v>0.5625</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="12">
         <v>0.5714</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="12">
         <v>0.4815</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="12">
         <v>0.4634</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="12">
         <v>0.4898</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="12">
         <v>0.463</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="12">
         <v>0.377</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="12">
         <v>0.3387</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="12">
         <v>0.3265</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="12">
         <v>0.3056</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="12">
         <v>0.2075</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="Q22" s="12">
         <v>0.2615</v>
       </c>
-      <c r="R22" s="10">
+      <c r="R22" s="12">
         <v>0.232</v>
       </c>
-      <c r="S22" s="10">
+      <c r="S22" s="12">
         <v>0.1443</v>
       </c>
-      <c r="T22" s="10">
-        <v>0.0617</v>
-      </c>
-      <c r="U22" s="11">
-        <v>0.0986</v>
-      </c>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10">
+      <c r="T22" s="13">
+        <v>0.1014</v>
+      </c>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.13415</v>
+        <v>0.1592333333</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1748,7 +1748,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="12"/>
+      <c r="W27" s="14"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1806,8 +1806,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="13"/>
-      <c r="W28" s="12"/>
+      <c r="T28" s="15"/>
+      <c r="W28" s="14"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1863,87 +1863,85 @@
       <c r="Q29" s="8">
         <v>0.2759</v>
       </c>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10">
+      <c r="R29" s="12"/>
+      <c r="S29" s="13">
         <v>0.1111</v>
       </c>
-      <c r="T29" s="15"/>
-      <c r="U29" s="10"/>
-      <c r="V29" s="10"/>
-      <c r="W29" s="10"/>
-      <c r="X29" s="10"/>
-      <c r="Y29" s="10"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
       <c r="Z29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12">
         <v>0.1333</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="12">
         <v>0.1667</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="12">
         <v>0.3514</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="12">
         <v>0.375</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="12">
         <v>0.3778</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="12">
         <v>0.3226</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="12">
         <v>0.4359</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="12">
         <v>0.4286</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="12">
         <v>0.4366</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="12">
         <v>0.3457</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="12">
         <v>0.3222</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="12">
         <v>0.2568</v>
       </c>
-      <c r="O30" s="10">
+      <c r="O30" s="12">
         <v>0.1905</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="12">
         <v>0.2281</v>
       </c>
-      <c r="Q30" s="10">
+      <c r="Q30" s="12">
         <v>0.3243</v>
       </c>
-      <c r="R30" s="10">
+      <c r="R30" s="12">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="10">
+      <c r="S30" s="12">
         <v>0.2308</v>
       </c>
-      <c r="T30" s="10">
-        <v>0.1304</v>
-      </c>
-      <c r="U30" s="11">
-        <v>0.08</v>
-      </c>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10"/>
-      <c r="Y30" s="10"/>
-      <c r="Z30" s="10">
+      <c r="T30" s="13">
+        <v>0.0784</v>
+      </c>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.192725</v>
+        <v>0.2129666667</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2068,7 +2066,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="12"/>
+      <c r="N34" s="14"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2254,89 +2252,87 @@
       <c r="Q37" s="8">
         <v>0.303</v>
       </c>
-      <c r="R37" s="10">
+      <c r="R37" s="12">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
-      <c r="U37" s="10"/>
-      <c r="V37" s="10"/>
-      <c r="W37" s="10"/>
-      <c r="X37" s="10"/>
-      <c r="Y37" s="10"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="12"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="12"/>
       <c r="Z37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="12">
         <v>0.4375</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="12">
         <v>0.4</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="12">
         <v>0.4</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="12">
         <v>0.4</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="12">
         <v>0.4167</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="12">
         <v>0.4</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="12">
         <v>0.4211</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="12">
         <v>0.451</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J38" s="12">
         <v>0.5161</v>
       </c>
-      <c r="K38" s="10">
+      <c r="K38" s="12">
         <v>0.5128</v>
       </c>
-      <c r="L38" s="10">
+      <c r="L38" s="12">
         <v>0.3913</v>
       </c>
-      <c r="M38" s="10">
+      <c r="M38" s="12">
         <v>0.46</v>
       </c>
-      <c r="N38" s="10">
+      <c r="N38" s="12">
         <v>0.325</v>
       </c>
-      <c r="O38" s="10">
+      <c r="O38" s="12">
         <v>0.3333</v>
       </c>
-      <c r="P38" s="10">
+      <c r="P38" s="12">
         <v>0.2564</v>
       </c>
-      <c r="Q38" s="10">
+      <c r="Q38" s="12">
         <v>0.3238</v>
       </c>
-      <c r="R38" s="10">
+      <c r="R38" s="12">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="10">
+      <c r="S38" s="12">
         <v>0.1974</v>
       </c>
-      <c r="T38" s="10">
-        <v>0.087</v>
-      </c>
-      <c r="U38" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="V38" s="10"/>
-      <c r="W38" s="10"/>
-      <c r="X38" s="10"/>
-      <c r="Y38" s="10"/>
-      <c r="Z38" s="10">
+      <c r="T38" s="13">
+        <v>0.125</v>
+      </c>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.1569</v>
+        <v>0.1885333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2465,7 +2461,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="12"/>
+      <c r="L44" s="14"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2491,7 +2487,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="16"/>
+      <c r="I45" s="18"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2509,65 +2505,63 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="10">
+      <c r="S45" s="13">
         <v>0.0714</v>
       </c>
-      <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
-      <c r="V45" s="10"/>
-      <c r="W45" s="10"/>
-      <c r="X45" s="10"/>
-      <c r="Y45" s="10"/>
-      <c r="Z45" s="10"/>
+      <c r="T45" s="12"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12"/>
+      <c r="Y45" s="12"/>
+      <c r="Z45" s="12"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12">
         <v>0.1111</v>
       </c>
-      <c r="Q46" s="10">
+      <c r="Q46" s="12">
         <v>0.2828</v>
       </c>
-      <c r="R46" s="10">
+      <c r="R46" s="12">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="10">
+      <c r="S46" s="12">
         <v>0.1705</v>
       </c>
-      <c r="T46" s="10">
-        <v>0.1429</v>
-      </c>
-      <c r="U46" s="11">
+      <c r="T46" s="13">
         <v>0.05</v>
       </c>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10"/>
-      <c r="X46" s="10"/>
-      <c r="Y46" s="10"/>
-      <c r="Z46" s="10">
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="12"/>
+      <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.157525</v>
+        <v>0.1624</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
+      <c r="Q47" s="12"/>
+      <c r="R47" s="12"/>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
@@ -2735,58 +2729,56 @@
       <c r="R53" s="8">
         <v>0.2857</v>
       </c>
-      <c r="S53" s="10">
+      <c r="S53" s="13">
         <v>0.122</v>
       </c>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
-      <c r="X53" s="10"/>
-      <c r="Y53" s="10"/>
-      <c r="Z53" s="10"/>
+      <c r="T53" s="12"/>
+      <c r="U53" s="12"/>
+      <c r="V53" s="12"/>
+      <c r="W53" s="12"/>
+      <c r="X53" s="12"/>
+      <c r="Y53" s="12"/>
+      <c r="Z53" s="12"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10">
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
+      <c r="P54" s="12"/>
+      <c r="Q54" s="12">
         <v>0.2727</v>
       </c>
-      <c r="R54" s="10">
+      <c r="R54" s="12">
         <v>0.296</v>
       </c>
-      <c r="S54" s="10">
+      <c r="S54" s="12">
         <v>0.192</v>
       </c>
-      <c r="T54" s="10">
-        <v>0.1504</v>
-      </c>
-      <c r="U54" s="11">
-        <v>0.1327</v>
-      </c>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10"/>
-      <c r="X54" s="10"/>
-      <c r="Y54" s="10"/>
-      <c r="Z54" s="10">
+      <c r="T54" s="13">
+        <v>0.125</v>
+      </c>
+      <c r="U54" s="12"/>
+      <c r="V54" s="12"/>
+      <c r="W54" s="12"/>
+      <c r="X54" s="12"/>
+      <c r="Y54" s="12"/>
+      <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.192775</v>
+        <v>0.2043333333</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -2826,7 +2818,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="12"/>
+      <c r="L58" s="14"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -2868,57 +2860,57 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
-      <c r="V61" s="10"/>
-      <c r="W61" s="10"/>
-      <c r="X61" s="10"/>
-      <c r="Y61" s="10"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
+      <c r="P61" s="12"/>
+      <c r="Q61" s="12"/>
+      <c r="R61" s="12"/>
+      <c r="S61" s="12"/>
+      <c r="T61" s="12"/>
+      <c r="U61" s="12"/>
+      <c r="V61" s="12"/>
+      <c r="W61" s="12"/>
+      <c r="X61" s="12"/>
+      <c r="Y61" s="12"/>
       <c r="Z61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
-      <c r="N62" s="10"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
-      <c r="Q62" s="10"/>
-      <c r="R62" s="10"/>
-      <c r="S62" s="10"/>
-      <c r="T62" s="10"/>
-      <c r="U62" s="10"/>
-      <c r="V62" s="10"/>
-      <c r="W62" s="10"/>
-      <c r="X62" s="10"/>
-      <c r="Y62" s="10"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="P62" s="12"/>
+      <c r="Q62" s="12"/>
+      <c r="R62" s="12"/>
+      <c r="S62" s="12"/>
+      <c r="T62" s="12"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12"/>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="12"/>
       <c r="Z62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -3097,8 +3089,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="17"/>
-      <c r="T65" s="17"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3197,71 +3189,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="18">
+      <c r="B67" s="20">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="18">
+      <c r="C67" s="20">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="18">
+      <c r="D67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="18">
+      <c r="E67" s="20">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="18">
+      <c r="F67" s="20">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="18">
+      <c r="G67" s="20">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="18">
+      <c r="H67" s="20">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="18">
+      <c r="I67" s="20">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="18">
+      <c r="J67" s="20">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="18">
+      <c r="K67" s="20">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="18">
+      <c r="L67" s="20">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="18">
+      <c r="M67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="18">
+      <c r="N67" s="20">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="18">
+      <c r="O67" s="20">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="18">
+      <c r="P67" s="20">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="18">
+      <c r="Q67" s="20">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="18">
+      <c r="R67" s="20">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3272,7 +3264,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="18">
+      <c r="Z67" s="20">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3365,85 +3357,85 @@
       <c r="A69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="12">
         <f t="shared" ref="B69:S69" si="13">average(B53,B45,B37,B29,B21,B13,B5)</f>
         <v>0.3444333333</v>
       </c>
-      <c r="C69" s="10">
+      <c r="C69" s="12">
         <f t="shared" si="13"/>
         <v>0.309525</v>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="12">
         <f t="shared" si="13"/>
         <v>0.42125</v>
       </c>
-      <c r="E69" s="10">
+      <c r="E69" s="12">
         <f t="shared" si="13"/>
         <v>0.42478</v>
       </c>
-      <c r="F69" s="10">
+      <c r="F69" s="12">
         <f t="shared" si="13"/>
         <v>0.40488</v>
       </c>
-      <c r="G69" s="10">
+      <c r="G69" s="12">
         <f t="shared" si="13"/>
         <v>0.45414</v>
       </c>
-      <c r="H69" s="10">
+      <c r="H69" s="12">
         <f t="shared" si="13"/>
         <v>0.40556</v>
       </c>
-      <c r="I69" s="10">
+      <c r="I69" s="12">
         <f t="shared" si="13"/>
         <v>0.31688</v>
       </c>
-      <c r="J69" s="10">
+      <c r="J69" s="12">
         <f t="shared" si="13"/>
         <v>0.41248</v>
       </c>
-      <c r="K69" s="10">
+      <c r="K69" s="12">
         <f t="shared" si="13"/>
         <v>0.29162</v>
       </c>
-      <c r="L69" s="10">
+      <c r="L69" s="12">
         <f t="shared" si="13"/>
         <v>0.35694</v>
       </c>
-      <c r="M69" s="10">
+      <c r="M69" s="12">
         <f t="shared" si="13"/>
         <v>0.3687333333</v>
       </c>
-      <c r="N69" s="10">
+      <c r="N69" s="12">
         <f t="shared" si="13"/>
         <v>0.26642</v>
       </c>
-      <c r="O69" s="10">
+      <c r="O69" s="12">
         <f t="shared" si="13"/>
         <v>0.2291666667</v>
       </c>
-      <c r="P69" s="10">
+      <c r="P69" s="12">
         <f t="shared" si="13"/>
         <v>0.3634</v>
       </c>
-      <c r="Q69" s="10">
+      <c r="Q69" s="12">
         <f t="shared" si="13"/>
         <v>0.2847571429</v>
       </c>
-      <c r="R69" s="10">
+      <c r="R69" s="12">
         <f t="shared" si="13"/>
         <v>0.15246</v>
       </c>
-      <c r="S69" s="10">
+      <c r="S69" s="12">
         <f t="shared" si="13"/>
         <v>0.1193333333</v>
       </c>
-      <c r="T69" s="10"/>
+      <c r="T69" s="12"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
-      <c r="Z69" s="10">
+      <c r="Z69" s="12">
         <f>average(R69:Y69)</f>
         <v>0.1358966667</v>
       </c>
@@ -3452,85 +3444,81 @@
       <c r="A70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="10">
-        <f t="shared" ref="B70:U70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+      <c r="B70" s="12">
+        <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
-      <c r="C70" s="10">
+      <c r="C70" s="12">
         <f t="shared" si="14"/>
         <v>0.366525</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="12">
         <f t="shared" si="14"/>
         <v>0.30455</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E70" s="12">
         <f t="shared" si="14"/>
         <v>0.38494</v>
       </c>
-      <c r="F70" s="10">
+      <c r="F70" s="12">
         <f t="shared" si="14"/>
         <v>0.40984</v>
       </c>
-      <c r="G70" s="10">
+      <c r="G70" s="12">
         <f t="shared" si="14"/>
         <v>0.4393</v>
       </c>
-      <c r="H70" s="10">
+      <c r="H70" s="12">
         <f t="shared" si="14"/>
         <v>0.42082</v>
       </c>
-      <c r="I70" s="10">
+      <c r="I70" s="12">
         <f t="shared" si="14"/>
         <v>0.4131</v>
       </c>
-      <c r="J70" s="10">
+      <c r="J70" s="12">
         <f t="shared" si="14"/>
         <v>0.3999</v>
       </c>
-      <c r="K70" s="10">
+      <c r="K70" s="12">
         <f t="shared" si="14"/>
         <v>0.38592</v>
       </c>
-      <c r="L70" s="10">
+      <c r="L70" s="12">
         <f t="shared" si="14"/>
         <v>0.33754</v>
       </c>
-      <c r="M70" s="10">
+      <c r="M70" s="12">
         <f t="shared" si="14"/>
         <v>0.34014</v>
       </c>
-      <c r="N70" s="10">
+      <c r="N70" s="12">
         <f t="shared" si="14"/>
         <v>0.30044</v>
       </c>
-      <c r="O70" s="10">
+      <c r="O70" s="12">
         <f t="shared" si="14"/>
         <v>0.30184</v>
       </c>
-      <c r="P70" s="10">
+      <c r="P70" s="12">
         <f t="shared" si="14"/>
         <v>0.2368833333</v>
       </c>
-      <c r="Q70" s="10">
+      <c r="Q70" s="12">
         <f t="shared" si="14"/>
         <v>0.3044714286</v>
       </c>
-      <c r="R70" s="10">
+      <c r="R70" s="12">
         <f t="shared" si="14"/>
         <v>0.2830428571</v>
       </c>
-      <c r="S70" s="10">
+      <c r="S70" s="12">
         <f t="shared" si="14"/>
         <v>0.2062</v>
       </c>
-      <c r="T70" s="10">
+      <c r="T70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1249</v>
-      </c>
-      <c r="U70" s="10">
-        <f t="shared" si="14"/>
-        <v>0.1058571429</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3543,30 +3531,30 @@
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="1"/>
-      <c r="S79" s="10"/>
+      <c r="S79" s="12"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="1"/>
-      <c r="S80" s="10"/>
+      <c r="S80" s="12"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="1"/>
-      <c r="S81" s="10"/>
+      <c r="S81" s="12"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="1"/>
-      <c r="S82" s="10"/>
+      <c r="S82" s="12"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="1"/>
-      <c r="S83" s="10"/>
+      <c r="S83" s="12"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="1"/>
-      <c r="S84" s="10"/>
+      <c r="S84" s="12"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="S85" s="10"/>
+      <c r="S85" s="12"/>
     </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
@@ -3595,67 +3583,67 @@
       <c r="B109" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="10" t="str">
+      <c r="C109" s="12" t="str">
         <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D109" s="10" t="str">
+      <c r="D109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E109" s="10" t="str">
+      <c r="E109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F109" s="10" t="str">
+      <c r="F109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G109" s="10" t="str">
+      <c r="G109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H109" s="10" t="str">
+      <c r="H109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I109" s="10" t="str">
+      <c r="I109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J109" s="10" t="str">
+      <c r="J109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K109" s="10" t="str">
+      <c r="K109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L109" s="10" t="str">
+      <c r="L109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M109" s="10" t="str">
+      <c r="M109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N109" s="10" t="str">
+      <c r="N109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O109" s="10" t="str">
+      <c r="O109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P109" s="10" t="str">
+      <c r="P109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q109" s="10" t="str">
+      <c r="Q109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R109" s="10" t="str">
+      <c r="R109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -131,12 +131,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -165,6 +165,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -772,7 +775,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="13">
-        <v>0.1538</v>
+        <v>0.127</v>
       </c>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
@@ -781,13 +784,13 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2539714286</v>
+        <v>0.2501428571</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2">
@@ -919,7 +922,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="14"/>
+      <c r="W10" s="15"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -978,7 +981,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="14"/>
+      <c r="W11" s="15"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1036,7 +1039,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="14"/>
+      <c r="W12" s="15"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1100,8 +1103,8 @@
       <c r="S13" s="13">
         <v>0.16</v>
       </c>
-      <c r="T13" s="15"/>
-      <c r="W13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="W13" s="17"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
@@ -1163,7 +1166,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="13">
-        <v>0.1</v>
+        <v>0.0787</v>
       </c>
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
@@ -1172,12 +1175,12 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.2016666667</v>
+        <v>0.1945666667</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="S15" s="12"/>
-      <c r="T15" s="17"/>
+      <c r="T15" s="18"/>
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
@@ -1196,7 +1199,7 @@
       <c r="Z16" s="12"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="2">
@@ -1542,7 +1545,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="13">
-        <v>0.1014</v>
+        <v>0.1029</v>
       </c>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
@@ -1551,13 +1554,13 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1592333333</v>
+        <v>0.1597333333</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2">
@@ -1748,7 +1751,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="14"/>
+      <c r="W27" s="15"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1806,8 +1809,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="15"/>
-      <c r="W28" s="14"/>
+      <c r="T28" s="16"/>
+      <c r="W28" s="15"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1867,7 +1870,7 @@
       <c r="S29" s="13">
         <v>0.1111</v>
       </c>
-      <c r="T29" s="17"/>
+      <c r="T29" s="18"/>
       <c r="U29" s="12"/>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
@@ -1947,7 +1950,7 @@
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B33" s="2">
@@ -2066,7 +2069,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="14"/>
+      <c r="N34" s="15"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2323,7 +2326,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="13">
-        <v>0.125</v>
+        <v>0.1667</v>
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="12"/>
@@ -2332,13 +2335,13 @@
       <c r="Y38" s="12"/>
       <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.1885333333</v>
+        <v>0.2024333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="14" t="s">
         <v>11</v>
       </c>
       <c r="B41" s="2">
@@ -2461,7 +2464,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="14"/>
+      <c r="L44" s="15"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2487,7 +2490,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="18"/>
+      <c r="I45" s="19"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2547,7 +2550,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="13">
-        <v>0.05</v>
+        <v>0.0263</v>
       </c>
       <c r="U46" s="12"/>
       <c r="V46" s="12"/>
@@ -2556,7 +2559,7 @@
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.1624</v>
+        <v>0.1545</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2565,7 +2568,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B49" s="2">
@@ -2769,7 +2772,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="13">
-        <v>0.125</v>
+        <v>0.1226</v>
       </c>
       <c r="U54" s="12"/>
       <c r="V54" s="12"/>
@@ -2778,13 +2781,13 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.2043333333</v>
+        <v>0.2035333333</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="1"/>
+      <c r="A57" s="14"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -2818,7 +2821,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="14"/>
+      <c r="L58" s="15"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -3089,8 +3092,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="19"/>
-      <c r="T65" s="19"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="20"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3189,71 +3192,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="21">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="20">
+      <c r="C67" s="21">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="21">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="21">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="21">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="20">
+      <c r="G67" s="21">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="20">
+      <c r="H67" s="21">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="20">
+      <c r="I67" s="21">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="20">
+      <c r="J67" s="21">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="20">
+      <c r="K67" s="21">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="20">
+      <c r="L67" s="21">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="20">
+      <c r="M67" s="21">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="20">
+      <c r="N67" s="21">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="20">
+      <c r="O67" s="21">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="20">
+      <c r="P67" s="21">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="20">
+      <c r="Q67" s="21">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="20">
+      <c r="R67" s="21">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3264,7 +3267,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="20">
+      <c r="Z67" s="21">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3518,7 +3521,7 @@
       </c>
       <c r="T70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1048</v>
+        <v>0.1003714286</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3530,27 +3533,27 @@
     <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="B79" s="1"/>
+      <c r="B79" s="14"/>
       <c r="S79" s="12"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="B80" s="1"/>
+      <c r="B80" s="14"/>
       <c r="S80" s="12"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="B81" s="1"/>
+      <c r="B81" s="14"/>
       <c r="S81" s="12"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="1"/>
+      <c r="B82" s="14"/>
       <c r="S82" s="12"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="1"/>
+      <c r="B83" s="14"/>
       <c r="S83" s="12"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="B84" s="1"/>
+      <c r="B84" s="14"/>
       <c r="S84" s="12"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -777,14 +777,16 @@
       <c r="T6" s="13">
         <v>0.127</v>
       </c>
-      <c r="U6" s="12"/>
+      <c r="U6" s="13">
+        <v>0.125</v>
+      </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2501428571</v>
+        <v>0.2345</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,14 +1170,16 @@
       <c r="T14" s="13">
         <v>0.0787</v>
       </c>
-      <c r="U14" s="12"/>
+      <c r="U14" s="13">
+        <v>0.069</v>
+      </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.1945666667</v>
+        <v>0.163175</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1547,14 +1551,16 @@
       <c r="T22" s="13">
         <v>0.1029</v>
       </c>
-      <c r="U22" s="12"/>
+      <c r="U22" s="13">
+        <v>0.1045</v>
+      </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1597333333</v>
+        <v>0.145925</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1937,14 +1943,16 @@
       <c r="T30" s="13">
         <v>0.0784</v>
       </c>
-      <c r="U30" s="12"/>
+      <c r="U30" s="13">
+        <v>0.1053</v>
+      </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.2129666667</v>
+        <v>0.18605</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2328,14 +2336,16 @@
       <c r="T38" s="13">
         <v>0.1667</v>
       </c>
-      <c r="U38" s="12"/>
+      <c r="U38" s="13">
+        <v>0.2</v>
+      </c>
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
       <c r="X38" s="12"/>
       <c r="Y38" s="12"/>
       <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.2024333333</v>
+        <v>0.201825</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2552,14 +2562,16 @@
       <c r="T46" s="13">
         <v>0.0263</v>
       </c>
-      <c r="U46" s="12"/>
+      <c r="U46" s="13">
+        <v>0.0286</v>
+      </c>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.1545</v>
+        <v>0.123025</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2774,14 +2786,16 @@
       <c r="T54" s="13">
         <v>0.1226</v>
       </c>
-      <c r="U54" s="12"/>
+      <c r="U54" s="13">
+        <v>0.1171</v>
+      </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
       <c r="X54" s="12"/>
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.2035333333</v>
+        <v>0.181925</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -131,12 +131,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
+      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -165,9 +165,6 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -778,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.125</v>
+        <v>0.1333</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -786,13 +783,13 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2345</v>
+        <v>0.2355375</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2">
@@ -924,7 +921,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="15"/>
+      <c r="W10" s="14"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -983,7 +980,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="15"/>
+      <c r="W11" s="14"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1041,7 +1038,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="15"/>
+      <c r="W12" s="14"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1105,8 +1102,8 @@
       <c r="S13" s="13">
         <v>0.16</v>
       </c>
-      <c r="T13" s="16"/>
-      <c r="W13" s="17"/>
+      <c r="T13" s="15"/>
+      <c r="W13" s="16"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
@@ -1171,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.069</v>
+        <v>0.0682</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1179,12 +1176,12 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.163175</v>
+        <v>0.162975</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="S15" s="12"/>
-      <c r="T15" s="18"/>
+      <c r="T15" s="17"/>
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
@@ -1203,7 +1200,7 @@
       <c r="Z16" s="12"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="2">
@@ -1552,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.1045</v>
+        <v>0.1094</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1560,13 +1557,13 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.145925</v>
+        <v>0.14715</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2">
@@ -1757,7 +1754,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="15"/>
+      <c r="W27" s="14"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1815,8 +1812,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="16"/>
-      <c r="W28" s="15"/>
+      <c r="T28" s="15"/>
+      <c r="W28" s="14"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1876,7 +1873,7 @@
       <c r="S29" s="13">
         <v>0.1111</v>
       </c>
-      <c r="T29" s="18"/>
+      <c r="T29" s="17"/>
       <c r="U29" s="12"/>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
@@ -1944,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.1053</v>
+        <v>0.1091</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1952,13 +1949,13 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.18605</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B33" s="2">
@@ -2077,7 +2074,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="15"/>
+      <c r="N34" s="14"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2337,7 +2334,7 @@
         <v>0.1667</v>
       </c>
       <c r="U38" s="13">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
@@ -2345,13 +2342,13 @@
       <c r="Y38" s="12"/>
       <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.201825</v>
+        <v>0.276825</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B41" s="2">
@@ -2474,7 +2471,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="15"/>
+      <c r="L44" s="14"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2500,7 +2497,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="19"/>
+      <c r="I45" s="18"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2563,7 +2560,7 @@
         <v>0.0263</v>
       </c>
       <c r="U46" s="13">
-        <v>0.0286</v>
+        <v>0.0263</v>
       </c>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
@@ -2571,7 +2568,7 @@
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.123025</v>
+        <v>0.12245</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2580,7 +2577,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B49" s="2">
@@ -2787,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.1171</v>
+        <v>0.1111</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2795,13 +2792,13 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.181925</v>
+        <v>0.180425</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="14"/>
+      <c r="A57" s="1"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -2835,7 +2832,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="15"/>
+      <c r="L58" s="14"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -3106,8 +3103,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="20"/>
-      <c r="T65" s="20"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3206,71 +3203,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="21">
+      <c r="B67" s="20">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="21">
+      <c r="C67" s="20">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="21">
+      <c r="D67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="21">
+      <c r="E67" s="20">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="21">
+      <c r="F67" s="20">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="21">
+      <c r="G67" s="20">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="21">
+      <c r="H67" s="20">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="21">
+      <c r="I67" s="20">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="21">
+      <c r="J67" s="20">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="21">
+      <c r="K67" s="20">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="21">
+      <c r="L67" s="20">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="21">
+      <c r="M67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="21">
+      <c r="N67" s="20">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="21">
+      <c r="O67" s="20">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="21">
+      <c r="P67" s="20">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="21">
+      <c r="Q67" s="20">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="21">
+      <c r="R67" s="20">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3281,7 +3278,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="21">
+      <c r="Z67" s="20">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3462,7 +3459,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="12">
-        <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <f t="shared" ref="B70:U70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
       <c r="C70" s="12">
@@ -3536,6 +3533,10 @@
       <c r="T70" s="12">
         <f t="shared" si="14"/>
         <v>0.1003714286</v>
+      </c>
+      <c r="U70" s="12">
+        <f t="shared" si="14"/>
+        <v>0.1510571429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3547,27 +3548,27 @@
     <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="B79" s="14"/>
+      <c r="B79" s="1"/>
       <c r="S79" s="12"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="B80" s="14"/>
+      <c r="B80" s="1"/>
       <c r="S80" s="12"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="B81" s="14"/>
+      <c r="B81" s="1"/>
       <c r="S81" s="12"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="14"/>
+      <c r="B82" s="1"/>
       <c r="S82" s="12"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="14"/>
+      <c r="B83" s="1"/>
       <c r="S83" s="12"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="B84" s="14"/>
+      <c r="B84" s="1"/>
       <c r="S84" s="12"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">

--- a/public/Archive/pm-contract-data.xlsx
+++ b/public/Archive/pm-contract-data.xlsx
@@ -173,8 +173,8 @@
     <xf borderId="2" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -775,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.1333</v>
+        <v>0.1452</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -783,7 +783,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2355375</v>
+        <v>0.237025</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.0682</v>
+        <v>0.0698</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1176,7 +1176,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.162975</v>
+        <v>0.163375</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1549,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.1094</v>
+        <v>0.1129</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1557,7 +1557,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.14715</v>
+        <v>0.148025</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1941,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.1091</v>
+        <v>0.1034</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1949,7 +1949,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.187</v>
+        <v>0.185575</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2784,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.1111</v>
+        <v>0.1215</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2792,7 +2792,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.180425</v>
+        <v>0.183025</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="U70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1510571429</v>
+        <v>0.1541571429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
